--- a/Oyacachi-Guacamayos/iWUE_OYC_GUA.xlsx
+++ b/Oyacachi-Guacamayos/iWUE_OYC_GUA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X153"/>
+  <dimension ref="A1:Y150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,6 +544,11 @@
           <t>species5</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -555,10 +560,8 @@
       <c r="C2" t="n">
         <v>4039</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D2" t="n">
+        <v>82</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -607,7 +610,6 @@
           <t>p82-4039</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>Solanum stenophyllum</t>
@@ -623,9 +625,6 @@
           <t>stenophyllum</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -637,10 +636,8 @@
       <c r="C3" t="n">
         <v>4020</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D3" t="n">
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -655,7 +652,6 @@
       <c r="G3" t="n">
         <v>56069</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>45.78185494527062</v>
       </c>
@@ -687,7 +683,6 @@
           <t>p81-4020</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -703,9 +698,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -717,10 +709,8 @@
       <c r="C4" t="n">
         <v>4021</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D4" t="n">
+        <v>81</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -735,7 +725,6 @@
       <c r="G4" t="n">
         <v>56070</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>45.85056560902917</v>
       </c>
@@ -767,7 +756,6 @@
           <t>p81-4021</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -783,9 +771,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -797,10 +782,8 @@
       <c r="C5" t="n">
         <v>4022</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D5" t="n">
+        <v>81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -815,7 +798,6 @@
       <c r="G5" t="n">
         <v>56071</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>43.99153645459705</v>
       </c>
@@ -847,7 +829,6 @@
           <t>p81-4022</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -863,9 +844,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -877,10 +855,8 @@
       <c r="C6" t="n">
         <v>4027</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D6" t="n">
+        <v>81</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -895,7 +871,6 @@
       <c r="G6" t="n">
         <v>56073</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>45.93526033556084</v>
       </c>
@@ -927,7 +902,6 @@
           <t>p81-4027</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -943,9 +917,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -957,10 +928,8 @@
       <c r="C7" t="n">
         <v>4034</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D7" t="n">
+        <v>82</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -975,7 +944,6 @@
       <c r="G7" t="n">
         <v>56074</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>44.50739680752388</v>
       </c>
@@ -1007,7 +975,6 @@
           <t>p82-4034</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>Gynoxis induta</t>
@@ -1023,9 +990,6 @@
           <t>induta</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1037,10 +1001,8 @@
       <c r="C8" t="n">
         <v>4035</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D8" t="n">
+        <v>82</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1055,7 +1017,6 @@
       <c r="G8" t="n">
         <v>56075</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>45.68813628266524</v>
       </c>
@@ -1087,7 +1048,6 @@
           <t>p82-4035</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -1103,9 +1063,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1117,10 +1074,8 @@
       <c r="C9" t="n">
         <v>4038</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D9" t="n">
+        <v>82</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1135,7 +1090,6 @@
       <c r="G9" t="n">
         <v>56076</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>44.8272916274702</v>
       </c>
@@ -1167,7 +1121,6 @@
           <t>p82-4038</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>Solanum stenophyllum</t>
@@ -1183,9 +1136,6 @@
           <t>stenophyllum</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1197,10 +1147,8 @@
       <c r="C10" t="n">
         <v>4043</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D10" t="n">
+        <v>82</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1215,9 +1163,6 @@
       <c r="G10" t="n">
         <v>56078</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>2.47063005938469</v>
       </c>
@@ -1243,7 +1188,6 @@
           <t>p82-4043</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -1259,9 +1203,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1273,10 +1214,8 @@
       <c r="C11" t="n">
         <v>4044</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D11" t="n">
+        <v>82</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1291,7 +1230,6 @@
       <c r="G11" t="n">
         <v>56079</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>44.99950540509508</v>
       </c>
@@ -1323,7 +1261,6 @@
           <t>p82-4044</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>Gynoxis cf acostae</t>
@@ -1344,8 +1281,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1357,10 +1292,8 @@
       <c r="C12" t="n">
         <v>4045</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D12" t="n">
+        <v>82</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1375,7 +1308,6 @@
       <c r="G12" t="n">
         <v>56080</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>43.84988184998212</v>
       </c>
@@ -1407,7 +1339,6 @@
           <t>p82-4045</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -1423,9 +1354,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1437,10 +1365,8 @@
       <c r="C13" t="n">
         <v>4046</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D13" t="n">
+        <v>82</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1455,7 +1381,6 @@
       <c r="G13" t="n">
         <v>56081</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>45.49</v>
       </c>
@@ -1510,8 +1435,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1523,10 +1446,8 @@
       <c r="C14" t="n">
         <v>4050</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D14" t="n">
+        <v>82</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1541,7 +1462,6 @@
       <c r="G14" t="n">
         <v>56082</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>45.81181702871249</v>
       </c>
@@ -1573,7 +1493,6 @@
           <t>p82-4050</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -1589,9 +1508,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1603,10 +1519,8 @@
       <c r="C15" t="n">
         <v>4100</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D15" t="n">
+        <v>85</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1621,7 +1535,6 @@
       <c r="G15" t="n">
         <v>56094</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>44.81877897413047</v>
       </c>
@@ -1653,7 +1566,6 @@
           <t>p85-4100</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Verbesina</t>
@@ -1664,10 +1576,6 @@
           <t>Verbesina</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1679,10 +1587,8 @@
       <c r="C16" t="n">
         <v>4101</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D16" t="n">
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1697,7 +1603,6 @@
       <c r="G16" t="n">
         <v>56095</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>44.96473740003615</v>
       </c>
@@ -1729,7 +1634,6 @@
           <t>p85-4101</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Verbesina</t>
@@ -1740,10 +1644,6 @@
           <t>Verbesina</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1755,10 +1655,8 @@
       <c r="C17" t="n">
         <v>4105</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D17" t="n">
+        <v>85</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1773,7 +1671,6 @@
       <c r="G17" t="n">
         <v>56096</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
         <v>44.20571555230563</v>
       </c>
@@ -1805,7 +1702,6 @@
           <t>p85-4105</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Seesea crasivenosa</t>
@@ -1821,9 +1717,6 @@
           <t>crasivenosa</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1835,10 +1728,8 @@
       <c r="C18" t="n">
         <v>4106</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D18" t="n">
+        <v>85</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1853,7 +1744,6 @@
       <c r="G18" t="n">
         <v>56097</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>44.26933269854089</v>
       </c>
@@ -1885,7 +1775,6 @@
           <t>p85-4106</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>Verbesina</t>
@@ -1896,10 +1785,6 @@
           <t>Verbesina</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1911,10 +1796,8 @@
       <c r="C19" t="n">
         <v>4110</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D19" t="n">
+        <v>85</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1929,7 +1812,6 @@
       <c r="G19" t="n">
         <v>56098</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>43.86223879426386</v>
       </c>
@@ -1961,7 +1843,6 @@
           <t>p85-4110</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>Seesea crasivenosa</t>
@@ -1977,9 +1858,6 @@
           <t>crasivenosa</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1991,10 +1869,8 @@
       <c r="C20" t="n">
         <v>4115</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D20" t="n">
+        <v>85</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -2009,7 +1885,6 @@
       <c r="G20" t="n">
         <v>56099</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>45.42878404532536</v>
       </c>
@@ -2041,7 +1916,6 @@
           <t>p85-4115</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>Verbesina</t>
@@ -2052,10 +1926,6 @@
           <t>Verbesina</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2067,10 +1937,8 @@
       <c r="C21" t="n">
         <v>4240</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D21" t="n">
+        <v>83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2085,7 +1953,6 @@
       <c r="G21" t="n">
         <v>56121</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>45.26921958553201</v>
       </c>
@@ -2117,7 +1984,6 @@
           <t>p83-4240</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -2133,9 +1999,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2147,10 +2010,8 @@
       <c r="C22" t="n">
         <v>4241</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D22" t="n">
+        <v>83</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2165,7 +2026,6 @@
       <c r="G22" t="n">
         <v>56122</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>45.20780688123111</v>
       </c>
@@ -2197,7 +2057,6 @@
           <t>p83-4241</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -2213,9 +2072,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2227,10 +2083,8 @@
       <c r="C23" t="n">
         <v>4242</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D23" t="n">
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2245,7 +2099,6 @@
       <c r="G23" t="n">
         <v>56123</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>44.44448289608685</v>
       </c>
@@ -2277,7 +2130,6 @@
           <t>p83-4242</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -2293,9 +2145,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2307,10 +2156,8 @@
       <c r="C24" t="n">
         <v>4244</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D24" t="n">
+        <v>83</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2325,7 +2172,6 @@
       <c r="G24" t="n">
         <v>56124</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>45.02795254274201</v>
       </c>
@@ -2357,7 +2203,6 @@
           <t>p83-4244</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -2373,9 +2218,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2387,10 +2229,8 @@
       <c r="C25" t="n">
         <v>4248</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D25" t="n">
+        <v>83</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2405,7 +2245,6 @@
       <c r="G25" t="n">
         <v>56126</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>45.68162440093023</v>
       </c>
@@ -2437,7 +2276,6 @@
           <t>p83-4248</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -2453,9 +2291,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2467,10 +2302,8 @@
       <c r="C26" t="n">
         <v>4249</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D26" t="n">
+        <v>83</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2485,9 +2318,6 @@
       <c r="G26" t="n">
         <v>56127</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="n">
         <v>2.49931722525938</v>
       </c>
@@ -2513,7 +2343,6 @@
           <t>p83-4249</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -2529,9 +2358,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2543,10 +2369,8 @@
       <c r="C27" t="n">
         <v>4250</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D27" t="n">
+        <v>83</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2561,7 +2385,6 @@
       <c r="G27" t="n">
         <v>56128</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>45.08798083524663</v>
       </c>
@@ -2593,7 +2416,6 @@
           <t>p83-4250</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -2609,9 +2431,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2623,10 +2442,8 @@
       <c r="C28" t="n">
         <v>157</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D28" t="n">
+        <v>6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2638,8 +2455,6 @@
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>33.23899805693006</v>
       </c>
@@ -2671,7 +2486,6 @@
           <t>p06-8186</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>Sapium stylare</t>
@@ -2687,9 +2501,6 @@
           <t>stylare</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2701,10 +2512,8 @@
       <c r="C29" t="n">
         <v>161</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D29" t="n">
+        <v>6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2716,8 +2525,6 @@
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>46.21458177218584</v>
       </c>
@@ -2749,7 +2556,6 @@
           <t>p06-8194</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>Guarea kunthiana</t>
@@ -2765,9 +2571,6 @@
           <t>kunthiana</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2779,10 +2582,8 @@
       <c r="C30" t="n">
         <v>161</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D30" t="n">
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2794,8 +2595,6 @@
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>46.21458177218584</v>
       </c>
@@ -2827,7 +2626,6 @@
           <t>p06-8194</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>Guarea kunthiana</t>
@@ -2843,9 +2641,6 @@
           <t>kunthiana</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2857,10 +2652,8 @@
       <c r="C31" t="n">
         <v>158</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D31" t="n">
+        <v>6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2872,8 +2665,6 @@
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>44.27375288947213</v>
       </c>
@@ -2905,7 +2696,6 @@
           <t>p06-8188</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>Dussia tessmanniii</t>
@@ -2921,9 +2711,6 @@
           <t>tessmanniii</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2935,10 +2722,8 @@
       <c r="C32" t="n">
         <v>151</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D32" t="n">
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2950,8 +2735,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
         <v>43.85</v>
       </c>
@@ -2996,10 +2779,6 @@
           <t>Posoqueria</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3011,10 +2790,8 @@
       <c r="C33" t="n">
         <v>178</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="D33" t="n">
+        <v>7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3026,8 +2803,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
         <v>44.15718100926103</v>
       </c>
@@ -3059,7 +2834,6 @@
           <t>p07-8147</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>Chomelia tenuiflora</t>
@@ -3075,9 +2849,6 @@
           <t>tenuiflora</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -3089,10 +2860,8 @@
       <c r="C34" t="n">
         <v>186</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="D34" t="n">
+        <v>7</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3104,8 +2873,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
         <v>46.17</v>
       </c>
@@ -3155,9 +2922,6 @@
           <t>karstenii</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3169,10 +2933,8 @@
       <c r="C35" t="n">
         <v>218</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="D35" t="n">
+        <v>8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3184,8 +2946,6 @@
           <t>Melastomataceae</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
         <v>45.54213094035732</v>
       </c>
@@ -3217,7 +2977,6 @@
           <t>p08-8136</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>Miconia glandulistyla</t>
@@ -3233,9 +2992,6 @@
           <t>glandulistyla</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3247,10 +3003,8 @@
       <c r="C36" t="n">
         <v>214</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="D36" t="n">
+        <v>8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -3262,8 +3016,6 @@
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
         <v>45.93956862030475</v>
       </c>
@@ -3295,7 +3047,6 @@
           <t>p08-8135</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>Cryptocarya</t>
@@ -3306,10 +3057,6 @@
           <t>Cryptocarya</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -3321,10 +3068,8 @@
       <c r="C37" t="n">
         <v>209</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="D37" t="n">
+        <v>8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3336,8 +3081,6 @@
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
         <v>44.39762420055948</v>
       </c>
@@ -3369,7 +3112,6 @@
           <t>p08-8133</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>Ruagea cf ovalis</t>
@@ -3390,8 +3132,6 @@
           <t>ovalis</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3403,10 +3143,8 @@
       <c r="C38" t="n">
         <v>1645</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="D38" t="n">
+        <v>55</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3418,8 +3156,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
         <v>43.53127007787473</v>
       </c>
@@ -3451,7 +3187,6 @@
           <t>p55-8120</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>Palicourea demissa</t>
@@ -3467,9 +3202,6 @@
           <t>demissa</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3481,10 +3213,8 @@
       <c r="C39" t="n">
         <v>1648</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="D39" t="n">
+        <v>55</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3496,8 +3226,6 @@
           <t>Chloranthaceae</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
         <v>44.97329961361584</v>
       </c>
@@ -3529,7 +3257,6 @@
           <t>p55-8123</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>Hedyosmum cuatrecazanum</t>
@@ -3545,9 +3272,6 @@
           <t>cuatrecazanum</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -3559,10 +3283,8 @@
       <c r="C40" t="n">
         <v>1649</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="D40" t="n">
+        <v>55</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3574,8 +3296,6 @@
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>44.67065684895357</v>
       </c>
@@ -3607,7 +3327,6 @@
           <t>p55-8122</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>Ruagea glabra</t>
@@ -3623,9 +3342,6 @@
           <t>glabra</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3637,10 +3353,8 @@
       <c r="C41" t="n">
         <v>4039</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D41" t="n">
+        <v>82</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3652,8 +3366,6 @@
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="n">
         <v>43.65307755435455</v>
       </c>
@@ -3685,7 +3397,6 @@
           <t>p82-4039</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>Solanum stenophyllum</t>
@@ -3701,9 +3412,6 @@
           <t>stenophyllum</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3715,10 +3423,8 @@
       <c r="C42" t="n">
         <v>4020</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D42" t="n">
+        <v>81</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3730,8 +3436,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
         <v>44.44205714996029</v>
       </c>
@@ -3763,7 +3467,6 @@
           <t>p81-8016</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -3779,9 +3482,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3793,10 +3493,8 @@
       <c r="C43" t="n">
         <v>4021</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D43" t="n">
+        <v>81</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3808,10 +3506,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="n">
         <v>2.02159852497584</v>
       </c>
@@ -3837,7 +3531,6 @@
           <t>p81-8013</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -3853,9 +3546,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3867,10 +3557,8 @@
       <c r="C44" t="n">
         <v>4022</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D44" t="n">
+        <v>81</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3882,8 +3570,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
         <v>46.24958928586945</v>
       </c>
@@ -3915,7 +3601,6 @@
           <t>p81-8039</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -3931,9 +3616,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3945,10 +3627,8 @@
       <c r="C45" t="n">
         <v>4027</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D45" t="n">
+        <v>81</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3960,8 +3640,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
         <v>44.17087954499277</v>
       </c>
@@ -3993,7 +3671,6 @@
           <t>p81-8052</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -4009,9 +3686,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4023,10 +3697,8 @@
       <c r="C46" t="n">
         <v>4034</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D46" t="n">
+        <v>82</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -4038,8 +3710,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
         <v>44.62413839400409</v>
       </c>
@@ -4071,7 +3741,6 @@
           <t>p82-4034</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>Gynoxis induta</t>
@@ -4087,9 +3756,6 @@
           <t>induta</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4101,10 +3767,8 @@
       <c r="C47" t="n">
         <v>4035</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D47" t="n">
+        <v>82</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4116,8 +3780,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
         <v>44.53016936884806</v>
       </c>
@@ -4149,7 +3811,6 @@
           <t>p82-4036</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -4165,9 +3826,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -4179,10 +3837,8 @@
       <c r="C48" t="n">
         <v>4038</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D48" t="n">
+        <v>82</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4194,8 +3850,6 @@
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
         <v>57.73299333090606</v>
       </c>
@@ -4227,7 +3881,6 @@
           <t>p82-4038</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>Solanum stenophyllum</t>
@@ -4243,9 +3896,6 @@
           <t>stenophyllum</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4257,10 +3907,8 @@
       <c r="C49" t="n">
         <v>4043</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D49" t="n">
+        <v>82</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -4272,8 +3920,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
         <v>43.37382012740808</v>
       </c>
@@ -4305,7 +3951,6 @@
           <t>p82-8080</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -4321,9 +3966,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -4335,10 +3977,8 @@
       <c r="C50" t="n">
         <v>4044</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D50" t="n">
+        <v>82</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -4350,8 +3990,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
         <v>44.35045479681124</v>
       </c>
@@ -4383,7 +4021,6 @@
           <t>p82-4044</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>Gynoxis cf acostae</t>
@@ -4404,8 +4041,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -4417,10 +4052,8 @@
       <c r="C51" t="n">
         <v>4045</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D51" t="n">
+        <v>82</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -4432,8 +4065,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>43.65516023355507</v>
       </c>
@@ -4465,7 +4096,6 @@
           <t>p82-4045</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -4481,9 +4111,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -4495,10 +4122,8 @@
       <c r="C52" t="n">
         <v>4046</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D52" t="n">
+        <v>82</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -4510,8 +4135,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="n">
         <v>45.49</v>
       </c>
@@ -4566,8 +4189,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -4579,10 +4200,8 @@
       <c r="C53" t="n">
         <v>4050</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="D53" t="n">
+        <v>82</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -4594,8 +4213,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
         <v>44.47170098265144</v>
       </c>
@@ -4627,7 +4244,6 @@
           <t>p82-4050</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -4643,9 +4259,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -4657,10 +4270,8 @@
       <c r="C54" t="n">
         <v>4055</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D54" t="n">
+        <v>83</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -4672,8 +4283,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
         <v>45.27483755431948</v>
       </c>
@@ -4705,7 +4314,6 @@
           <t>p83-4055</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -4721,9 +4329,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -4735,10 +4340,8 @@
       <c r="C55" t="n">
         <v>4100</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D55" t="n">
+        <v>85</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -4750,10 +4353,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="n">
         <v>2.63914808226952</v>
       </c>
@@ -4779,7 +4378,6 @@
           <t>p85-8066</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>Verbesina</t>
@@ -4790,10 +4388,6 @@
           <t>Verbesina</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -4805,10 +4399,8 @@
       <c r="C56" t="n">
         <v>4101</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D56" t="n">
+        <v>85</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -4820,8 +4412,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
         <v>32.49087325546191</v>
       </c>
@@ -4853,7 +4443,6 @@
           <t>p85-8067</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>Verbesina</t>
@@ -4864,10 +4453,6 @@
           <t>Verbesina</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -4879,10 +4464,8 @@
       <c r="C57" t="n">
         <v>4105</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D57" t="n">
+        <v>85</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -4894,8 +4477,6 @@
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
         <v>44.43103925466794</v>
       </c>
@@ -4927,7 +4508,6 @@
           <t>p85-8071</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>Seesea crasivenosa</t>
@@ -4943,9 +4523,6 @@
           <t>crasivenosa</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -4957,10 +4534,8 @@
       <c r="C58" t="n">
         <v>4106</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D58" t="n">
+        <v>85</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -4972,8 +4547,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
         <v>44.99131881377813</v>
       </c>
@@ -5005,7 +4578,6 @@
           <t>p85-8076</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>Verbesina</t>
@@ -5016,10 +4588,6 @@
           <t>Verbesina</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5031,10 +4599,8 @@
       <c r="C59" t="n">
         <v>4110</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D59" t="n">
+        <v>85</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -5046,10 +4612,6 @@
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
         <v>2.46851625746442</v>
       </c>
@@ -5075,7 +4637,6 @@
           <t>p85-4110</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>Seesea crasivenosa</t>
@@ -5091,9 +4652,6 @@
           <t>crasivenosa</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5105,10 +4663,8 @@
       <c r="C60" t="n">
         <v>4112</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D60" t="n">
+        <v>85</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -5120,8 +4676,6 @@
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
         <v>46.97</v>
       </c>
@@ -5171,9 +4725,6 @@
           <t>crasivenosa</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5185,10 +4736,8 @@
       <c r="C61" t="n">
         <v>4115</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D61" t="n">
+        <v>85</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -5200,8 +4749,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
         <v>43.34641726956603</v>
       </c>
@@ -5233,7 +4780,6 @@
           <t>p85-8072</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>Verbesina</t>
@@ -5244,10 +4790,6 @@
           <t>Verbesina</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -5259,10 +4801,8 @@
       <c r="C62" t="n">
         <v>4240</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D62" t="n">
+        <v>83</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -5274,8 +4814,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>45.35364468497561</v>
       </c>
@@ -5307,7 +4845,6 @@
           <t>p83-4240</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -5323,9 +4860,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -5337,10 +4871,8 @@
       <c r="C63" t="n">
         <v>4241</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D63" t="n">
+        <v>83</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -5352,8 +4884,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
         <v>45.37628256952662</v>
       </c>
@@ -5385,7 +4915,6 @@
           <t>p83-4241</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -5401,9 +4930,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -5415,10 +4941,8 @@
       <c r="C64" t="n">
         <v>4242</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D64" t="n">
+        <v>83</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -5430,8 +4954,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
         <v>43.12477906874004</v>
       </c>
@@ -5463,7 +4985,6 @@
           <t>p83-4242</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -5479,9 +5000,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -5493,10 +5011,8 @@
       <c r="C65" t="n">
         <v>4244</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D65" t="n">
+        <v>83</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -5508,8 +5024,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
         <v>44.0322432633165</v>
       </c>
@@ -5541,7 +5055,6 @@
           <t>p83-8068</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -5557,9 +5070,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -5571,10 +5081,8 @@
       <c r="C66" t="n">
         <v>4248</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D66" t="n">
+        <v>83</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -5586,8 +5094,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>43.11260137057986</v>
       </c>
@@ -5619,7 +5125,6 @@
           <t>p83-4248</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -5635,9 +5140,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -5649,10 +5151,8 @@
       <c r="C67" t="n">
         <v>4249</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D67" t="n">
+        <v>83</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -5664,8 +5164,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
         <v>45.22457855032971</v>
       </c>
@@ -5697,7 +5195,6 @@
           <t>p83-4249</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -5713,9 +5210,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -5727,10 +5221,8 @@
       <c r="C68" t="n">
         <v>4250</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D68" t="n">
+        <v>83</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -5742,8 +5234,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
         <v>44.59872112610041</v>
       </c>
@@ -5775,7 +5265,6 @@
           <t>p83-4250</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -5791,9 +5280,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -5802,11 +5288,8 @@
       <c r="B69" t="n">
         <v>8023</v>
       </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D69" t="n">
+        <v>81</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -5818,8 +5301,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
         <v>44.04395189751652</v>
       </c>
@@ -5851,7 +5332,6 @@
           <t>p81-8023</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -5867,9 +5347,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -5878,11 +5355,8 @@
       <c r="B70" t="n">
         <v>8034</v>
       </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D70" t="n">
+        <v>81</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -5894,8 +5368,6 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
         <v>42.62488416383843</v>
       </c>
@@ -5927,7 +5399,6 @@
           <t>p81-8034</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
           <t>Polylepis pauta</t>
@@ -5943,9 +5414,6 @@
           <t>pauta</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -5954,11 +5422,8 @@
       <c r="B71" t="n">
         <v>8056</v>
       </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D71" t="n">
+        <v>81</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -5970,8 +5435,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
         <v>46.12463283982211</v>
       </c>
@@ -6003,7 +5466,6 @@
           <t>p81-8056</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -6019,9 +5481,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -6030,11 +5489,8 @@
       <c r="B72" t="n">
         <v>8035</v>
       </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="D72" t="n">
+        <v>81</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -6046,8 +5502,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
         <v>46.91994218877939</v>
       </c>
@@ -6079,7 +5533,6 @@
           <t>p81-8035</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
           <t>Gynoxis acostae</t>
@@ -6095,9 +5548,6 @@
           <t>acostae</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -6106,11 +5556,8 @@
       <c r="B73" t="n">
         <v>8073</v>
       </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
+      <c r="D73" t="n">
+        <v>85</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -6122,8 +5569,6 @@
           <t>Solanaceae</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
         <v>33.20193208428898</v>
       </c>
@@ -6155,7 +5600,6 @@
           <t>p85-8073</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
           <t>Seesea crasivenosa</t>
@@ -6171,9 +5615,6 @@
           <t>crasivenosa</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -6185,10 +5626,8 @@
       <c r="C74" t="n">
         <v>143</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D74" t="n">
+        <v>6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -6200,8 +5639,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
         <v>43.41817128946882</v>
       </c>
@@ -6233,7 +5670,6 @@
           <t>p06-8203</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr">
         <is>
           <t>Palicourea stenosepala</t>
@@ -6249,9 +5685,6 @@
           <t>stenosepala</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -6263,10 +5696,8 @@
       <c r="C75" t="n">
         <v>148</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D75" t="n">
+        <v>6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -6278,8 +5709,6 @@
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
         <v>41.44488708014945</v>
       </c>
@@ -6311,7 +5740,6 @@
           <t>p06-8181</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>Ficus tonduzi</t>
@@ -6327,9 +5755,6 @@
           <t>tonduzi</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -6341,10 +5766,8 @@
       <c r="C76" t="n">
         <v>169</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D76" t="n">
+        <v>6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -6356,8 +5779,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
         <v>45.3285601335725</v>
       </c>
@@ -6389,7 +5810,6 @@
           <t>p06-8200</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>Critoniopsis cf occidentalis</t>
@@ -6410,8 +5830,6 @@
           <t>occidentalis</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -6423,10 +5841,8 @@
       <c r="C77" t="n">
         <v>169</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+      <c r="D77" t="n">
+        <v>6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -6438,8 +5854,6 @@
           <t>Asteraceae</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
         <v>45.3285601335725</v>
       </c>
@@ -6471,7 +5885,6 @@
           <t>p06-8200</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>Critoniopsis cf occidentalis</t>
@@ -6492,8 +5905,6 @@
           <t>occidentalis</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -6505,10 +5916,8 @@
       <c r="C78" t="n">
         <v>183</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="D78" t="n">
+        <v>7</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -6520,8 +5929,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
         <v>24.41813760506811</v>
       </c>
@@ -6553,7 +5960,6 @@
           <t>p07-8150</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>Joosia ulei</t>
@@ -6569,9 +5975,6 @@
           <t>ulei</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -6583,10 +5986,8 @@
       <c r="C79" t="n">
         <v>184</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="D79" t="n">
+        <v>7</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -6598,8 +5999,6 @@
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
         <v>43.72</v>
       </c>
@@ -6649,9 +6048,6 @@
           <t>andinum</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -6663,10 +6059,8 @@
       <c r="C80" t="n">
         <v>191</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="D80" t="n">
+        <v>7</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -6678,8 +6072,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
         <v>45.36583922537127</v>
       </c>
@@ -6711,7 +6103,6 @@
           <t>p07-8152</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>Joosia ulei</t>
@@ -6727,9 +6118,6 @@
           <t>ulei</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -6741,10 +6129,8 @@
       <c r="C81" t="n">
         <v>199</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="D81" t="n">
+        <v>7</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -6756,8 +6142,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
         <v>19.51971950360319</v>
       </c>
@@ -6789,7 +6173,6 @@
           <t>p07-8158</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>Joosia ulei</t>
@@ -6805,9 +6188,6 @@
           <t>ulei</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -6819,10 +6199,8 @@
       <c r="C82" t="n">
         <v>202</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="D82" t="n">
+        <v>8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -6834,8 +6212,6 @@
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
         <v>45.83156140342884</v>
       </c>
@@ -6867,7 +6243,6 @@
           <t>p08-8140</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>Guarea kunthiana</t>
@@ -6883,9 +6258,6 @@
           <t>kunthiana</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -6897,10 +6269,8 @@
       <c r="C83" t="n">
         <v>203</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="D83" t="n">
+        <v>8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -6912,8 +6282,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
         <v>45.00310488018739</v>
       </c>
@@ -6945,7 +6313,6 @@
           <t>p08-8130</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>Faramea oblongifolia</t>
@@ -6961,9 +6328,6 @@
           <t>oblongifolia</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -6975,10 +6339,8 @@
       <c r="C84" t="n">
         <v>208</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="D84" t="n">
+        <v>8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -6990,8 +6352,6 @@
           <t>Phyllanthaceae</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
         <v>45.43275844816041</v>
       </c>
@@ -7023,7 +6383,6 @@
           <t>p08-8132</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>Hieronyma oblonga</t>
@@ -7039,9 +6398,6 @@
           <t>oblonga</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -7053,10 +6409,8 @@
       <c r="C85" t="n">
         <v>210</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="D85" t="n">
+        <v>8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -7068,8 +6422,6 @@
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
         <v>42.50813358848679</v>
       </c>
@@ -7101,7 +6453,6 @@
           <t>p08-8141</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>Erythrina edulis</t>
@@ -7117,9 +6468,6 @@
           <t>edulis</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -7131,10 +6479,8 @@
       <c r="C86" t="n">
         <v>212</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+      <c r="D86" t="n">
+        <v>8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -7146,8 +6492,6 @@
           <t>Cunoniaceae</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
         <v>42.45340238453527</v>
       </c>
@@ -7179,7 +6523,6 @@
           <t>p08-8139</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>Weinmania pinnta</t>
@@ -7195,9 +6538,6 @@
           <t>pinnta</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -7209,10 +6549,8 @@
       <c r="C87" t="n">
         <v>1643</v>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="D87" t="n">
+        <v>55</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -7224,8 +6562,6 @@
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
         <v>45.64830763373875</v>
       </c>
@@ -7257,7 +6593,6 @@
           <t>p55-8107</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr">
         <is>
           <t>Annona sp.</t>
@@ -7273,9 +6608,6 @@
           <t>sp.</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -7287,10 +6619,8 @@
       <c r="C88" t="n">
         <v>1647</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="D88" t="n">
+        <v>55</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -7302,8 +6632,6 @@
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
         <v>45.04146477234478</v>
       </c>
@@ -7335,7 +6663,6 @@
           <t>p55-8124</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>Nectandra laurel</t>
@@ -7351,9 +6678,6 @@
           <t>laurel</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -7365,10 +6689,8 @@
       <c r="C89" t="n">
         <v>1678</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="D89" t="n">
+        <v>55</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -7380,8 +6702,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
         <v>43.46309389912029</v>
       </c>
@@ -7413,7 +6733,6 @@
           <t>p55-8106</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>Farameo oblongifolia</t>
@@ -7429,9 +6748,6 @@
           <t>oblongifolia</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -7440,11 +6756,8 @@
       <c r="B90" t="n">
         <v>8154</v>
       </c>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+      <c r="D90" t="n">
+        <v>7</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -7456,8 +6769,6 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="n">
         <v>45.06</v>
       </c>
@@ -7507,114 +6818,160 @@
           <t>ulei</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>&lt;NA&gt;</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8186</v>
+      </c>
+      <c r="C91" t="n">
+        <v>157</v>
+      </c>
+      <c r="D91" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Guacamayos</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Euphorbiaceae</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>1689</v>
+      </c>
       <c r="I91" t="n">
-        <v>59.86184817443561</v>
+        <v>42.43403731205088</v>
       </c>
       <c r="J91" t="n">
-        <v>-29.97</v>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+        <v>-25.51</v>
+      </c>
+      <c r="K91" t="n">
+        <v>3.35792397709957</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1.907002486103961</v>
+      </c>
+      <c r="M91" t="n">
+        <v>41.9211470613874</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-27.333327292607</v>
+      </c>
       <c r="O91" t="n">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>leaf pulverized</t>
+          <t>herbarium</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>p&lt;NA&gt;-&lt;NA&gt;</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
+          <t>p06-1689.0</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Sapium stylare</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Sapium</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>stylare</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>&lt;NA&gt;</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8182</v>
+      </c>
+      <c r="C92" t="n">
+        <v>151</v>
+      </c>
+      <c r="D92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Guacamayos</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1711</v>
+      </c>
       <c r="I92" t="n">
-        <v>55.6041384873765</v>
+        <v>45.36050104245147</v>
       </c>
       <c r="J92" t="n">
-        <v>-27</v>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+        <v>-30.28</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1.9960066613919</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.7565317128472872</v>
+      </c>
+      <c r="M92" t="n">
+        <v>42.5940452089312</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-31.0695419485989</v>
+      </c>
       <c r="O92" t="n">
-        <v>2023</v>
+        <v>2005</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>leaf pulverized</t>
+          <t>herbarium</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>p&lt;NA&gt;-&lt;NA&gt;</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
+          <t>p06-1711.0</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Posoqueria</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Posoqueria</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B93" t="n">
-        <v>8186</v>
+        <v>8147</v>
       </c>
       <c r="C93" t="n">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -7623,30 +6980,29 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="H93" t="n">
-        <v>1689</v>
+        <v>1715</v>
       </c>
       <c r="I93" t="n">
-        <v>42.43403731205088</v>
+        <v>44.53377308181305</v>
       </c>
       <c r="J93" t="n">
-        <v>-25.51</v>
+        <v>-31.16</v>
       </c>
       <c r="K93" t="n">
-        <v>3.35792397709957</v>
+        <v>2.76589785410334</v>
       </c>
       <c r="L93" t="n">
-        <v>1.907002486103961</v>
+        <v>2.185417454873428</v>
       </c>
       <c r="M93" t="n">
-        <v>41.9211470613874</v>
+        <v>44.3716948156506</v>
       </c>
       <c r="N93" t="n">
-        <v>-27.333327292607</v>
+        <v>-31.4928774116967</v>
       </c>
       <c r="O93" t="n">
         <v>2005</v>
@@ -7658,41 +7014,37 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>p06-1689.0</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
+          <t>p07-1715.0</t>
+        </is>
+      </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Sapium stylare</t>
+          <t>Chomelia tenuiflora</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Sapium</t>
+          <t>Chomelia</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>stylare</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
+          <t>tenuiflora</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B94" t="n">
-        <v>8182</v>
+        <v>8151</v>
       </c>
       <c r="C94" t="n">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -7704,27 +7056,26 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>1711</v>
+        <v>1738</v>
       </c>
       <c r="I94" t="n">
-        <v>45.36050104245147</v>
+        <v>45.43278144278158</v>
       </c>
       <c r="J94" t="n">
-        <v>-30.28</v>
+        <v>-29.17</v>
       </c>
       <c r="K94" t="n">
-        <v>1.9960066613919</v>
+        <v>2.05313341264609</v>
       </c>
       <c r="L94" t="n">
-        <v>0.7565317128472872</v>
+        <v>2.249046444807238</v>
       </c>
       <c r="M94" t="n">
-        <v>42.5940452089312</v>
+        <v>46.5643441491692</v>
       </c>
       <c r="N94" t="n">
-        <v>-31.0695419485989</v>
+        <v>-31.6879728105795</v>
       </c>
       <c r="O94" t="n">
         <v>2005</v>
@@ -7736,37 +7087,37 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>p06-1711.0</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
+          <t>p07-1738.0</t>
+        </is>
+      </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Posoqueria</t>
+          <t>Elaegia karstenii</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>Posoqueria</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
+          <t>Elaegia</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>karstenii</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B95" t="n">
-        <v>8147</v>
+        <v>8120</v>
       </c>
       <c r="C95" t="n">
-        <v>178</v>
+        <v>1645</v>
       </c>
       <c r="D95" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -7778,30 +7129,29 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>1715</v>
+        <v>3150</v>
       </c>
       <c r="I95" t="n">
-        <v>44.53377308181305</v>
+        <v>45.44247503782463</v>
       </c>
       <c r="J95" t="n">
-        <v>-31.16</v>
+        <v>-30.3</v>
       </c>
       <c r="K95" t="n">
-        <v>2.76589785410334</v>
+        <v>3.04470840861578</v>
       </c>
       <c r="L95" t="n">
-        <v>2.185417454873428</v>
+        <v>3.191434428553005</v>
       </c>
       <c r="M95" t="n">
-        <v>44.3716948156506</v>
+        <v>38.7143490808578</v>
       </c>
       <c r="N95" t="n">
-        <v>-31.4928774116967</v>
+        <v>-30.7132437884008</v>
       </c>
       <c r="O95" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -7810,41 +7160,37 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>p07-1715.0</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
+          <t>p55-3150.0</t>
+        </is>
+      </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Chomelia tenuiflora</t>
+          <t>Palicourea demissa</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Chomelia</t>
+          <t>Palicourea</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>tenuiflora</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
+          <t>demissa</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B96" t="n">
-        <v>8151</v>
+        <v>8123</v>
       </c>
       <c r="C96" t="n">
-        <v>186</v>
+        <v>1648</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -7853,33 +7199,32 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
+          <t>Chloranthaceae</t>
+        </is>
+      </c>
       <c r="H96" t="n">
-        <v>1738</v>
+        <v>3151</v>
       </c>
       <c r="I96" t="n">
-        <v>45.43278144278158</v>
+        <v>43.72773338949531</v>
       </c>
       <c r="J96" t="n">
-        <v>-29.17</v>
+        <v>-26.87</v>
       </c>
       <c r="K96" t="n">
-        <v>2.05313341264609</v>
+        <v>2.43575765718819</v>
       </c>
       <c r="L96" t="n">
-        <v>2.249046444807238</v>
+        <v>1.405574275634229</v>
       </c>
       <c r="M96" t="n">
-        <v>46.5643441491692</v>
+        <v>40.4955029803786</v>
       </c>
       <c r="N96" t="n">
-        <v>-31.6879728105795</v>
+        <v>-29.2663074760755</v>
       </c>
       <c r="O96" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -7888,76 +7233,71 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>p07-1738.0</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
+          <t>p55-3151.0</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Elaegia karstenii</t>
+          <t>Hedyosmum cuatrecazanum</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>Elaegia</t>
+          <t>Hedyosmum</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>karstenii</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
+          <t>cuatrecazanum</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B97" t="n">
-        <v>8120</v>
+        <v>4039</v>
       </c>
       <c r="C97" t="n">
-        <v>1645</v>
+        <v>4039</v>
       </c>
       <c r="D97" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Guacamayos</t>
+          <t>Oyacachi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
+          <t>Solanaceae</t>
+        </is>
+      </c>
       <c r="H97" t="n">
-        <v>3150</v>
+        <v>4194</v>
       </c>
       <c r="I97" t="n">
-        <v>45.44247503782463</v>
+        <v>44.2214859274287</v>
       </c>
       <c r="J97" t="n">
-        <v>-30.3</v>
+        <v>-27.29</v>
       </c>
       <c r="K97" t="n">
-        <v>3.04470840861578</v>
+        <v>3.46008158889689</v>
       </c>
       <c r="L97" t="n">
-        <v>3.191434428553005</v>
+        <v>5.333406134442499</v>
       </c>
       <c r="M97" t="n">
-        <v>38.7143490808578</v>
+        <v>45.94548483731</v>
       </c>
       <c r="N97" t="n">
-        <v>-30.7132437884008</v>
+        <v>-29.2231945725637</v>
       </c>
       <c r="O97" t="n">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -7966,41 +7306,37 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>p55-3150.0</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
+          <t>p82-4194.0</t>
+        </is>
+      </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Palicourea demissa</t>
+          <t>Solanum stenophyllum</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>Palicourea</t>
+          <t>Solanum</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>demissa</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
+          <t>stenophyllum</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B98" t="n">
-        <v>8123</v>
+        <v>8147</v>
       </c>
       <c r="C98" t="n">
-        <v>1648</v>
+        <v>178</v>
       </c>
       <c r="D98" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -8009,156 +7345,143 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chloranthaceae</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="n">
-        <v>3151</v>
+          <t>Rubiaceae</t>
+        </is>
       </c>
       <c r="I98" t="n">
-        <v>43.72773338949531</v>
+        <v>42.3153287103575</v>
       </c>
       <c r="J98" t="n">
-        <v>-26.87</v>
+        <v>-28.1463758657295</v>
       </c>
       <c r="K98" t="n">
-        <v>2.43575765718819</v>
+        <v>0.03102865446774084</v>
       </c>
       <c r="L98" t="n">
-        <v>1.405574275634229</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M98" t="n">
-        <v>40.4955029803786</v>
+        <v>0.5385279721197573</v>
       </c>
       <c r="N98" t="n">
-        <v>-29.2663074760755</v>
+        <v>-30.14</v>
       </c>
       <c r="O98" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>herbarium</t>
+          <t>leaf pulverized</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>p55-3151.0</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr"/>
+          <t>p07-178</t>
+        </is>
+      </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Hedyosmum cuatrecazanum</t>
+          <t>Chomelia tenuiflora</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Hedyosmum</t>
+          <t>Chomelia</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>cuatrecazanum</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
+          <t>tenuiflora</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B99" t="n">
-        <v>4039</v>
+        <v>8200</v>
       </c>
       <c r="C99" t="n">
-        <v>4039</v>
+        <v>169</v>
       </c>
       <c r="D99" t="n">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oyacachi</t>
+          <t>Guacamayos</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Solanaceae</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="n">
-        <v>4194</v>
+          <t>Asteraceae</t>
+        </is>
       </c>
       <c r="I99" t="n">
-        <v>44.2214859274287</v>
+        <v>44.1847568409624</v>
       </c>
       <c r="J99" t="n">
-        <v>-27.29</v>
+        <v>-28.2916676823504</v>
       </c>
       <c r="K99" t="n">
-        <v>3.46008158889689</v>
+        <v>0.03072015966621176</v>
       </c>
       <c r="L99" t="n">
-        <v>5.333406134442499</v>
+        <v>0.35</v>
       </c>
       <c r="M99" t="n">
-        <v>45.94548483731</v>
+        <v>0.4544398396122426</v>
       </c>
       <c r="N99" t="n">
-        <v>-29.2231945725637</v>
+        <v>-29.69</v>
       </c>
       <c r="O99" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>herbarium</t>
+          <t>leaf pulverized</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>p82-4194.0</t>
-        </is>
-      </c>
-      <c r="R99" t="inlineStr"/>
+          <t>p06-169</t>
+        </is>
+      </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Solanum stenophyllum</t>
+          <t>Critoniopsis cf occidentalis</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>Solanum</t>
+          <t>Critoniopsis</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>stenophyllum</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>occidentalis</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B100" t="n">
-        <v>8147</v>
+        <v>8141</v>
       </c>
       <c r="C100" t="n">
-        <v>178</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>210</v>
+      </c>
+      <c r="D100" t="n">
+        <v>8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -8167,28 +7490,26 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+          <t>Fabaceae</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>42.3153287103575</v>
+        <v>44.0493625260597</v>
       </c>
       <c r="J100" t="n">
-        <v>-28.1463758657295</v>
+        <v>-26.0088817121064</v>
       </c>
       <c r="K100" t="n">
-        <v>0.03102865446774084</v>
+        <v>0.02791351686241129</v>
       </c>
       <c r="L100" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.62</v>
       </c>
       <c r="M100" t="n">
-        <v>0.5385279721197573</v>
+        <v>0.4055964641710267</v>
       </c>
       <c r="N100" t="n">
-        <v>-30.14</v>
+        <v>-26.75</v>
       </c>
       <c r="O100" t="n">
         <v>2006</v>
@@ -8200,43 +7521,34 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>p07-178</t>
-        </is>
-      </c>
-      <c r="R100" t="inlineStr"/>
+          <t>p08-210</t>
+        </is>
+      </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Chomelia tenuiflora</t>
+          <t>Erythrina edulis</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>Chomelia</t>
+          <t>Erythrina</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>tenuiflora</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
+          <t>edulis</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B101" t="n">
-        <v>8200</v>
+        <v>101</v>
       </c>
       <c r="C101" t="n">
-        <v>169</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>185</v>
+      </c>
+      <c r="D101" t="n">
+        <v>7</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -8245,28 +7557,26 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Asteraceae</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>44.1847568409624</v>
+        <v>40.1267154082355</v>
       </c>
       <c r="J101" t="n">
-        <v>-28.2916676823504</v>
+        <v>-30.117772018719</v>
       </c>
       <c r="K101" t="n">
-        <v>0.03072015966621176</v>
+        <v>0.02715737349991614</v>
       </c>
       <c r="L101" t="n">
-        <v>0.35</v>
+        <v>1.68</v>
       </c>
       <c r="M101" t="n">
-        <v>0.4544398396122426</v>
+        <v>0.4338384329935683</v>
       </c>
       <c r="N101" t="n">
-        <v>-29.69</v>
+        <v>-31.72</v>
       </c>
       <c r="O101" t="n">
         <v>2006</v>
@@ -8278,47 +7588,37 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>p06-169</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr"/>
+          <t>p07-185</t>
+        </is>
+      </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Critoniopsis cf occidentalis</t>
+          <t>Joosia umbellifera</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>Critoniopsis</t>
+          <t>Joosia</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>cf</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>occidentalis</t>
-        </is>
-      </c>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
+          <t>umbellifera</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B102" t="n">
-        <v>8141</v>
+        <v>8158</v>
       </c>
       <c r="C102" t="n">
-        <v>210</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>199</v>
+      </c>
+      <c r="D102" t="n">
+        <v>7</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -8327,28 +7627,26 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>44.0493625260597</v>
+        <v>43.7224838903424</v>
       </c>
       <c r="J102" t="n">
-        <v>-26.0088817121064</v>
+        <v>-29.5928600653218</v>
       </c>
       <c r="K102" t="n">
-        <v>0.02791351686241129</v>
+        <v>0.0254395335967698</v>
       </c>
       <c r="L102" t="n">
-        <v>2.62</v>
+        <v>1.42</v>
       </c>
       <c r="M102" t="n">
-        <v>0.4055964641710267</v>
+        <v>0.4470760802662179</v>
       </c>
       <c r="N102" t="n">
-        <v>-26.75</v>
+        <v>-31.62</v>
       </c>
       <c r="O102" t="n">
         <v>2006</v>
@@ -8360,41 +7658,37 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>p08-210</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
+          <t>p07-199</t>
+        </is>
+      </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Erythrina edulis</t>
+          <t>Joosia umbellifera</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>Erythrina</t>
+          <t>Joosia</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>edulis</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
+          <t>umbellifera</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="B103" t="inlineStr"/>
+        <v>103</v>
+      </c>
+      <c r="B103" t="n">
+        <v>8159</v>
+      </c>
       <c r="C103" t="n">
-        <v>185</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>200</v>
+      </c>
+      <c r="D103" t="n">
+        <v>7</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -8403,28 +7697,26 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+          <t>Lauraceae</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>40.1267154082355</v>
+        <v>42.754053254055</v>
       </c>
       <c r="J103" t="n">
-        <v>-30.117772018719</v>
+        <v>-30.9552505558022</v>
       </c>
       <c r="K103" t="n">
-        <v>0.02715737349991614</v>
+        <v>0.01628815902121365</v>
       </c>
       <c r="L103" t="n">
-        <v>1.68</v>
+        <v>-0.11</v>
       </c>
       <c r="M103" t="n">
-        <v>0.4338384329935683</v>
+        <v>0.4858583549207572</v>
       </c>
       <c r="N103" t="n">
-        <v>-31.72</v>
+        <v>-32.63</v>
       </c>
       <c r="O103" t="n">
         <v>2006</v>
@@ -8436,43 +7728,47 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>p07-185</t>
-        </is>
-      </c>
-      <c r="R103" t="inlineStr"/>
+          <t>p07-200</t>
+        </is>
+      </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Joosia umbellifera</t>
+          <t>Aniba muca</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>Joosia</t>
+          <t>Aniba</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>umbellifera</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
+          <t>muca</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>coto</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Especie corregida de 'Aniba cf coto' a Aniba muca tras revisión taxonómica</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B104" t="n">
-        <v>8158</v>
+        <v>8130</v>
       </c>
       <c r="C104" t="n">
-        <v>199</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>203</v>
+      </c>
+      <c r="D104" t="n">
+        <v>8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -8484,25 +7780,23 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>43.7224838903424</v>
+        <v>43.6258099070622</v>
       </c>
       <c r="J104" t="n">
-        <v>-29.5928600653218</v>
+        <v>-30.9931125488299</v>
       </c>
       <c r="K104" t="n">
-        <v>0.0254395335967698</v>
+        <v>0.01773544441544489</v>
       </c>
       <c r="L104" t="n">
-        <v>1.42</v>
+        <v>-1.62</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4470760802662179</v>
+        <v>0.4031605311129898</v>
       </c>
       <c r="N104" t="n">
-        <v>-31.62</v>
+        <v>-31.9</v>
       </c>
       <c r="O104" t="n">
         <v>2006</v>
@@ -8514,41 +7808,34 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>p07-199</t>
-        </is>
-      </c>
-      <c r="R104" t="inlineStr"/>
+          <t>p08-203</t>
+        </is>
+      </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Joosia umbellifera</t>
+          <t>Faramea oblongifolia</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>Joosia</t>
+          <t>Faramea</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>umbellifera</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
+          <t>oblongifolia</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B105" t="inlineStr"/>
+        <v>105</v>
+      </c>
       <c r="C105" t="n">
-        <v>200</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>179</v>
+      </c>
+      <c r="D105" t="n">
+        <v>7</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -8557,28 +7844,26 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+          <t>Euphorbiaceae</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>42.754053254055</v>
+        <v>45.9375479511701</v>
       </c>
       <c r="J105" t="n">
-        <v>-30.9552505558022</v>
+        <v>-30.1010096700507</v>
       </c>
       <c r="K105" t="n">
-        <v>0.01628815902121365</v>
+        <v>0.0298852005898983</v>
       </c>
       <c r="L105" t="n">
-        <v>-0.11</v>
+        <v>7.87</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4858583549207572</v>
+        <v>0.4582454534910876</v>
       </c>
       <c r="N105" t="n">
-        <v>-32.63</v>
+        <v>-30.31</v>
       </c>
       <c r="O105" t="n">
         <v>2006</v>
@@ -8590,47 +7875,37 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>p07-200</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
+          <t>p07-179</t>
+        </is>
+      </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Aniba cf coto</t>
+          <t>Tetrorchidium andinum</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>Aniba</t>
+          <t>Tetrorchidium</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>cf</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>coto</t>
-        </is>
-      </c>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
+          <t>andinum</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B106" t="n">
-        <v>8130</v>
+        <v>8133</v>
       </c>
       <c r="C106" t="n">
-        <v>203</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>209</v>
+      </c>
+      <c r="D106" t="n">
+        <v>8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -8639,28 +7914,26 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+          <t>Meliaceae</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>43.6258099070622</v>
+        <v>44.4730895188967</v>
       </c>
       <c r="J106" t="n">
-        <v>-30.9931125488299</v>
+        <v>-29.2347173600147</v>
       </c>
       <c r="K106" t="n">
-        <v>0.01773544441544489</v>
+        <v>0.02643485797488288</v>
       </c>
       <c r="L106" t="n">
-        <v>-1.62</v>
+        <v>-0.14</v>
       </c>
       <c r="M106" t="n">
-        <v>0.4031605311129898</v>
+        <v>0.4473242003352184</v>
       </c>
       <c r="N106" t="n">
-        <v>-31.9</v>
+        <v>-30.32</v>
       </c>
       <c r="O106" t="n">
         <v>2006</v>
@@ -8672,41 +7945,32 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>p08-203</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
+          <t>p08-209</t>
+        </is>
+      </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Faramea oblongifolia</t>
+          <t>Ruagea</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Faramea</t>
-        </is>
-      </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>oblongifolia</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
+          <t>Ruagea</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B107" t="inlineStr"/>
+        <v>107</v>
+      </c>
+      <c r="B107" t="n">
+        <v>8182</v>
+      </c>
       <c r="C107" t="n">
-        <v>179</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>151</v>
+      </c>
+      <c r="D107" t="n">
+        <v>6</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -8715,28 +7979,26 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>45.9375479511701</v>
+        <v>44.9145959517734</v>
       </c>
       <c r="J107" t="n">
-        <v>-30.1010096700507</v>
+        <v>-27.645548665252</v>
       </c>
       <c r="K107" t="n">
-        <v>0.0298852005898983</v>
+        <v>0.01908125209516545</v>
       </c>
       <c r="L107" t="n">
-        <v>7.87</v>
+        <v>-0.39</v>
       </c>
       <c r="M107" t="n">
-        <v>0.4582454534910876</v>
+        <v>0.4544261445729605</v>
       </c>
       <c r="N107" t="n">
-        <v>-30.31</v>
+        <v>-28.77</v>
       </c>
       <c r="O107" t="n">
         <v>2006</v>
@@ -8748,43 +8010,34 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>p07-179</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
+          <t>p06-151</t>
+        </is>
+      </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>Tetrorchidium andinum</t>
+          <t>Posoqueria coriacea</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>Tetrorchidium</t>
+          <t>Posoqueria</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>andinum</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
+          <t>coriacea</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B108" t="n">
-        <v>8133</v>
+        <v>108</v>
       </c>
       <c r="C108" t="n">
-        <v>209</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>181</v>
+      </c>
+      <c r="D108" t="n">
+        <v>7</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -8793,28 +8046,14 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Meliaceae</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+          <t>Mimosaceae</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>44.4730895188967</v>
+        <v>46.3352144907804</v>
       </c>
       <c r="J108" t="n">
-        <v>-29.2347173600147</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0.02643485797488288</v>
-      </c>
-      <c r="L108" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0.4473242003352184</v>
-      </c>
-      <c r="N108" t="n">
-        <v>-30.32</v>
+        <v>-29.4868790363093</v>
       </c>
       <c r="O108" t="n">
         <v>2006</v>
@@ -8826,39 +8065,42 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>p08-209</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr"/>
+          <t>p07-181</t>
+        </is>
+      </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Ruagea</t>
+          <t>Inga sp. 1</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>Ruagea</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
+          <t>Inga</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>sp.</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B109" t="n">
-        <v>8182</v>
+        <v>8181</v>
       </c>
       <c r="C109" t="n">
-        <v>151</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>148</v>
+      </c>
+      <c r="D109" t="n">
+        <v>6</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -8867,28 +8109,26 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>44.9145959517734</v>
+        <v>40.6053715481823</v>
       </c>
       <c r="J109" t="n">
-        <v>-27.645548665252</v>
+        <v>-28.1121828530044</v>
       </c>
       <c r="K109" t="n">
-        <v>0.01908125209516545</v>
+        <v>0.03374045638880983</v>
       </c>
       <c r="L109" t="n">
-        <v>-0.39</v>
+        <v>0.4</v>
       </c>
       <c r="M109" t="n">
-        <v>0.4544261445729605</v>
+        <v>0.3723854771949546</v>
       </c>
       <c r="N109" t="n">
-        <v>-28.77</v>
+        <v>-29.35</v>
       </c>
       <c r="O109" t="n">
         <v>2006</v>
@@ -8900,41 +8140,37 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>p06-151</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
+          <t>p06-148</t>
+        </is>
+      </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Posoqueria coriacea</t>
+          <t>Ficus tonduzii</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>Posoqueria</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>coriacea</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
+          <t>tonduzii</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B110" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="B110" t="n">
+        <v>8203</v>
+      </c>
       <c r="C110" t="n">
-        <v>181</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>143</v>
+      </c>
+      <c r="D110" t="n">
+        <v>6</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -8943,21 +8179,27 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mimosaceae</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+          <t>Cunoniaceae</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>46.3352144907804</v>
+        <v>43.6652791109008</v>
       </c>
       <c r="J110" t="n">
-        <v>-29.4868790363093</v>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+        <v>-28.3727068118635</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.01619701636922634</v>
+      </c>
+      <c r="L110" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.4386066955354603</v>
+      </c>
+      <c r="N110" t="n">
+        <v>-30.11</v>
+      </c>
       <c r="O110" t="n">
         <v>2006</v>
       </c>
@@ -8968,47 +8210,34 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>p07-181</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
+          <t>p06-143</t>
+        </is>
+      </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Inga sp. 1</t>
+          <t>Weinmannia pinnata</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>Inga</t>
+          <t>Weinmannia</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>sp.</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
+          <t>pinnata</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B111" t="n">
-        <v>8181</v>
+        <v>111</v>
       </c>
       <c r="C111" t="n">
-        <v>148</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>142</v>
+      </c>
+      <c r="D111" t="n">
+        <v>6</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -9017,28 +8246,26 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Moraceae</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>40.6053715481823</v>
+        <v>42.8065750392793</v>
       </c>
       <c r="J111" t="n">
-        <v>-28.1121828530044</v>
+        <v>-27.0384835826904</v>
       </c>
       <c r="K111" t="n">
-        <v>0.03374045638880983</v>
+        <v>0.02692272714125975</v>
       </c>
       <c r="L111" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="M111" t="n">
-        <v>0.3723854771949546</v>
+        <v>0.4010560486178598</v>
       </c>
       <c r="N111" t="n">
-        <v>-29.35</v>
+        <v>-28.55</v>
       </c>
       <c r="O111" t="n">
         <v>2006</v>
@@ -9050,43 +8277,34 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>p06-148</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
+          <t>p06-142</t>
+        </is>
+      </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Ficus tonduzii</t>
+          <t>Palicourea stenosepala</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Ficus</t>
+          <t>Palicourea</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>tonduzii</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
+          <t>stenosepala</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B112" t="n">
-        <v>8203</v>
+        <v>112</v>
       </c>
       <c r="C112" t="n">
-        <v>143</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>182</v>
+      </c>
+      <c r="D112" t="n">
+        <v>7</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -9095,28 +8313,26 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cunoniaceae</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
+          <t>Lauraceae</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>43.6652791109008</v>
+        <v>43.6729653838469</v>
       </c>
       <c r="J112" t="n">
-        <v>-28.3727068118635</v>
+        <v>-30.6170064768113</v>
       </c>
       <c r="K112" t="n">
-        <v>0.01619701636922634</v>
+        <v>0.02315074402735965</v>
       </c>
       <c r="L112" t="n">
-        <v>-1.85</v>
+        <v>-0.37</v>
       </c>
       <c r="M112" t="n">
-        <v>0.4386066955354603</v>
+        <v>0.4541757418344188</v>
       </c>
       <c r="N112" t="n">
-        <v>-30.11</v>
+        <v>-31.86</v>
       </c>
       <c r="O112" t="n">
         <v>2006</v>
@@ -9128,41 +8344,37 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>p06-143</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr"/>
+          <t>p07-182</t>
+        </is>
+      </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Weinmannia pinnata</t>
+          <t>Endlicheria griseo-sericea</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Weinmannia</t>
+          <t>Endlicheria</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>pinnata</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
+          <t>griseo-sericea</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B113" t="inlineStr"/>
+        <v>113</v>
+      </c>
+      <c r="B113" t="n">
+        <v>8188</v>
+      </c>
       <c r="C113" t="n">
-        <v>142</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>158</v>
+      </c>
+      <c r="D113" t="n">
+        <v>6</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -9171,28 +8383,26 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+          <t>Anacardiaceae</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>42.8065750392793</v>
+        <v>44.9488330007575</v>
       </c>
       <c r="J113" t="n">
-        <v>-27.0384835826904</v>
+        <v>-29.8431956964564</v>
       </c>
       <c r="K113" t="n">
-        <v>0.02692272714125975</v>
+        <v>0.0259832691563732</v>
       </c>
       <c r="L113" t="n">
-        <v>0.59</v>
+        <v>-0.8</v>
       </c>
       <c r="M113" t="n">
-        <v>0.4010560486178598</v>
+        <v>0.4239248560247049</v>
       </c>
       <c r="N113" t="n">
-        <v>-28.55</v>
+        <v>-30.48</v>
       </c>
       <c r="O113" t="n">
         <v>2006</v>
@@ -9204,41 +8414,37 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>p06-142</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
+          <t>p06-158</t>
+        </is>
+      </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Palicourea stenosepala</t>
-        </is>
-      </c>
-      <c r="T113" t="inlineStr">
-        <is>
-          <t>Palicourea</t>
+          <t xml:space="preserve"> sp. 1</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>stenosepala</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
+          <t>sp.</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B114" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="B114" t="n">
+        <v>8188</v>
+      </c>
       <c r="C114" t="n">
-        <v>182</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>158</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -9247,28 +8453,26 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+          <t>Anacardiaceae</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>43.6729653838469</v>
+        <v>44.9488330007575</v>
       </c>
       <c r="J114" t="n">
-        <v>-30.6170064768113</v>
+        <v>-29.8431956964564</v>
       </c>
       <c r="K114" t="n">
-        <v>0.02315074402735965</v>
+        <v>0.02717910221519865</v>
       </c>
       <c r="L114" t="n">
-        <v>-0.37</v>
+        <v>-0.6823549684089606</v>
       </c>
       <c r="M114" t="n">
-        <v>0.4541757418344188</v>
+        <v>0.415862488670643</v>
       </c>
       <c r="N114" t="n">
-        <v>-31.86</v>
+        <v>-30.64109776078646</v>
       </c>
       <c r="O114" t="n">
         <v>2006</v>
@@ -9280,43 +8484,34 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>p07-182</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr"/>
+          <t>p06-158</t>
+        </is>
+      </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Endlicheria griseo-sericea</t>
-        </is>
-      </c>
-      <c r="T114" t="inlineStr">
-        <is>
-          <t>Endlicheria</t>
+          <t xml:space="preserve"> sp. 1</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>griseo-sericea</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
+          <t>sp.</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>113</v>
-      </c>
-      <c r="B115" t="n">
-        <v>8188</v>
+        <v>115</v>
       </c>
       <c r="C115" t="n">
-        <v>158</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>160</v>
+      </c>
+      <c r="D115" t="n">
+        <v>6</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -9325,28 +8520,26 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Anacardiaceae</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>44.9488330007575</v>
+        <v>43.5330956658599</v>
       </c>
       <c r="J115" t="n">
-        <v>-29.8431956964564</v>
+        <v>-30.3665936006202</v>
       </c>
       <c r="K115" t="n">
-        <v>0.0259832691563732</v>
+        <v>0.02185479141082021</v>
       </c>
       <c r="L115" t="n">
-        <v>-0.8</v>
+        <v>-1.14</v>
       </c>
       <c r="M115" t="n">
-        <v>0.4239248560247049</v>
+        <v>0.3875023156085859</v>
       </c>
       <c r="N115" t="n">
-        <v>-30.48</v>
+        <v>-30.82</v>
       </c>
       <c r="O115" t="n">
         <v>2006</v>
@@ -9358,43 +8551,37 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>p06-158</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr"/>
+          <t>p06-160</t>
+        </is>
+      </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t xml:space="preserve"> sp. 1</t>
-        </is>
-      </c>
-      <c r="T115" t="inlineStr"/>
+          <t>Palicourea stenosepala</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Palicourea</t>
+        </is>
+      </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>sp.</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
+          <t>stenosepala</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B116" t="n">
-        <v>8188</v>
+        <v>8194</v>
       </c>
       <c r="C116" t="n">
-        <v>158</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>161</v>
+      </c>
+      <c r="D116" t="n">
+        <v>6</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -9403,28 +8590,26 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Anacardiaceae</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+          <t>Meliaceae</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>44.9488330007575</v>
+        <v>41.5574282648701</v>
       </c>
       <c r="J116" t="n">
-        <v>-29.8431956964564</v>
+        <v>-30.2408233267637</v>
       </c>
       <c r="K116" t="n">
-        <v>0.02717910221519865</v>
+        <v>0.03133359278791505</v>
       </c>
       <c r="L116" t="n">
-        <v>-0.6823549684089606</v>
+        <v>-1.35</v>
       </c>
       <c r="M116" t="n">
-        <v>0.415862488670643</v>
+        <v>0.3946662160226899</v>
       </c>
       <c r="N116" t="n">
-        <v>-30.64109776078646</v>
+        <v>-30.44</v>
       </c>
       <c r="O116" t="n">
         <v>2006</v>
@@ -9436,41 +8621,37 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>p06-158</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr"/>
+          <t>p06-161</t>
+        </is>
+      </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t xml:space="preserve"> sp. 1</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr"/>
+          <t>Guarea kunthiana</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Guarea</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>sp.</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
+          <t>kunthiana</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="B117" t="inlineStr"/>
+        <v>117</v>
+      </c>
+      <c r="B117" t="n">
+        <v>8152</v>
+      </c>
       <c r="C117" t="n">
-        <v>160</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>190</v>
+      </c>
+      <c r="D117" t="n">
+        <v>7</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -9482,25 +8663,23 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>43.5330956658599</v>
+        <v>44.1375880953595</v>
       </c>
       <c r="J117" t="n">
-        <v>-30.3665936006202</v>
+        <v>-29.7346801098339</v>
       </c>
       <c r="K117" t="n">
-        <v>0.02185479141082021</v>
+        <v>0.02533905125836741</v>
       </c>
       <c r="L117" t="n">
-        <v>-1.14</v>
+        <v>2.33</v>
       </c>
       <c r="M117" t="n">
-        <v>0.3875023156085859</v>
+        <v>0.442407775568847</v>
       </c>
       <c r="N117" t="n">
-        <v>-30.82</v>
+        <v>-31.56</v>
       </c>
       <c r="O117" t="n">
         <v>2006</v>
@@ -9512,43 +8691,37 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>p06-160</t>
-        </is>
-      </c>
-      <c r="R117" t="inlineStr"/>
+          <t>p07-190</t>
+        </is>
+      </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Palicourea stenosepala</t>
+          <t>Joosia umbellifera</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>Palicourea</t>
+          <t>Joosia</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>stenosepala</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
+          <t>umbellifera</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B118" t="n">
-        <v>8194</v>
+        <v>8151</v>
       </c>
       <c r="C118" t="n">
-        <v>161</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>186</v>
+      </c>
+      <c r="D118" t="n">
+        <v>7</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -9557,28 +8730,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Meliaceae</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>41.5574282648701</v>
+        <v>44.4094427382361</v>
       </c>
       <c r="J118" t="n">
-        <v>-30.2408233267637</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0.03133359278791505</v>
-      </c>
-      <c r="L118" t="n">
-        <v>-1.35</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0.3946662160226899</v>
-      </c>
-      <c r="N118" t="n">
-        <v>-30.44</v>
+        <v>-28.4495364199884</v>
       </c>
       <c r="O118" t="n">
         <v>2006</v>
@@ -9590,41 +8749,42 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>p06-161</t>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr"/>
+          <t>p07-186</t>
+        </is>
+      </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>Guarea kunthiana</t>
+          <t>Elaeagia cf utilis</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>Guarea</t>
+          <t>Elaeagia</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>kunthiana</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>utilis</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>117</v>
-      </c>
-      <c r="B119" t="inlineStr"/>
+        <v>119</v>
+      </c>
+      <c r="B119" t="n">
+        <v>8132</v>
+      </c>
       <c r="C119" t="n">
-        <v>190</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>208</v>
+      </c>
+      <c r="D119" t="n">
+        <v>8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -9633,28 +8793,26 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+          <t>Euphorbiaceae</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>44.1375880953595</v>
+        <v>44.1670964148073</v>
       </c>
       <c r="J119" t="n">
-        <v>-29.7346801098339</v>
+        <v>-30.7662210097165</v>
       </c>
       <c r="K119" t="n">
-        <v>0.02533905125836741</v>
+        <v>0.01926120954130157</v>
       </c>
       <c r="L119" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="M119" t="n">
-        <v>0.442407775568847</v>
+        <v>0.423511587670453</v>
       </c>
       <c r="N119" t="n">
-        <v>-31.56</v>
+        <v>-31.89</v>
       </c>
       <c r="O119" t="n">
         <v>2006</v>
@@ -9666,43 +8824,49 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>p07-190</t>
-        </is>
-      </c>
-      <c r="R119" t="inlineStr"/>
+          <t>p08-208</t>
+        </is>
+      </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>Joosia umbellifera</t>
+          <t>Hyeronima sp 2 cf macrocarpa</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>Joosia</t>
+          <t>Hyeronima</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>umbellifera</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
+          <t>sp</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>macrocarpa</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="B120" t="n">
-        <v>8151</v>
+        <v>120</v>
       </c>
       <c r="C120" t="n">
-        <v>186</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>223</v>
+      </c>
+      <c r="D120" t="n">
+        <v>8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -9711,21 +8875,27 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+          <t>Icacinaceae</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>44.4094427382361</v>
+        <v>44.2617433800809</v>
       </c>
       <c r="J120" t="n">
-        <v>-28.4495364199884</v>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+        <v>-28.8814160780333</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.03544445873599856</v>
+      </c>
+      <c r="L120" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.450324943231333</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-29.51</v>
+      </c>
       <c r="O120" t="n">
         <v>2006</v>
       </c>
@@ -9736,47 +8906,37 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>p07-186</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
+          <t>p08-223</t>
+        </is>
+      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Elaeagia cf utilis</t>
+          <t>Calatola costaricensis</t>
         </is>
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>Elaeagia</t>
+          <t>Calatola</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>cf</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>utilis</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
+          <t>costaricensis</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B121" t="n">
-        <v>8132</v>
+        <v>8136</v>
       </c>
       <c r="C121" t="n">
-        <v>208</v>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>218</v>
+      </c>
+      <c r="D121" t="n">
+        <v>8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -9785,28 +8945,26 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+          <t>Melastomataceae</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>44.1670964148073</v>
+        <v>44.8795891422905</v>
       </c>
       <c r="J121" t="n">
-        <v>-30.7662210097165</v>
+        <v>-27.6152814359953</v>
       </c>
       <c r="K121" t="n">
-        <v>0.01926120954130157</v>
+        <v>0.01385853554463809</v>
       </c>
       <c r="L121" t="n">
-        <v>2.25</v>
+        <v>-1.79</v>
       </c>
       <c r="M121" t="n">
-        <v>0.423511587670453</v>
+        <v>0.4481561561002697</v>
       </c>
       <c r="N121" t="n">
-        <v>-31.89</v>
+        <v>-29.22</v>
       </c>
       <c r="O121" t="n">
         <v>2006</v>
@@ -9818,53 +8976,37 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>p08-208</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr"/>
+          <t>p08-218</t>
+        </is>
+      </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Hyeronima sp 2 cf macrocarpa</t>
+          <t>Miconia glandulistyla</t>
         </is>
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>Hyeronima</t>
+          <t>Miconia</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>sp</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>cf</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>macrocarpa</t>
+          <t>glandulistyla</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B122" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="B122" t="n">
+        <v>8136</v>
+      </c>
       <c r="C122" t="n">
-        <v>223</v>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>218</v>
+      </c>
+      <c r="D122" t="n">
+        <v>8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -9873,28 +9015,26 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Icacinaceae</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+          <t>Melastomataceae</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>44.2617433800809</v>
+        <v>44.8795891422905</v>
       </c>
       <c r="J122" t="n">
-        <v>-28.8814160780333</v>
+        <v>-27.6152814359953</v>
       </c>
       <c r="K122" t="n">
-        <v>0.03544445873599856</v>
+        <v>0.0128324732201899</v>
       </c>
       <c r="L122" t="n">
-        <v>-0.39</v>
+        <v>-1.986708788052843</v>
       </c>
       <c r="M122" t="n">
-        <v>0.450324943231333</v>
+        <v>0.4123187584396911</v>
       </c>
       <c r="N122" t="n">
-        <v>-29.51</v>
+        <v>-29.53430209877506</v>
       </c>
       <c r="O122" t="n">
         <v>2006</v>
@@ -9906,43 +9046,34 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>p08-223</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr"/>
+          <t>p08-218</t>
+        </is>
+      </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Calatola costaricensis</t>
+          <t>Miconia glandulistyla</t>
         </is>
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>Calatola</t>
+          <t>Miconia</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>costaricensis</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
+          <t>glandulistyla</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="B123" t="n">
-        <v>8136</v>
+        <v>123</v>
       </c>
       <c r="C123" t="n">
-        <v>218</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>222</v>
+      </c>
+      <c r="D123" t="n">
+        <v>8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -9951,28 +9082,26 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Melastomataceae</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
+          <t>Sapindaceae</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>44.8795891422905</v>
+        <v>44.4425917116135</v>
       </c>
       <c r="J123" t="n">
-        <v>-27.6152814359953</v>
+        <v>-26.7875784326478</v>
       </c>
       <c r="K123" t="n">
-        <v>0.01385853554463809</v>
+        <v>0.02482700425427824</v>
       </c>
       <c r="L123" t="n">
-        <v>-1.79</v>
+        <v>-0.7</v>
       </c>
       <c r="M123" t="n">
-        <v>0.4481561561002697</v>
+        <v>0.4659163218406722</v>
       </c>
       <c r="N123" t="n">
-        <v>-29.22</v>
+        <v>-29.01</v>
       </c>
       <c r="O123" t="n">
         <v>2006</v>
@@ -9984,43 +9113,37 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>p08-218</t>
-        </is>
-      </c>
-      <c r="R123" t="inlineStr"/>
+          <t>p08-222</t>
+        </is>
+      </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>Miconia glandulistyla</t>
+          <t>Allophylus floribundus</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>Miconia</t>
+          <t>Allophylus</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>glandulistyla</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
+          <t>floribundus</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B124" t="n">
-        <v>8136</v>
+        <v>8122</v>
       </c>
       <c r="C124" t="n">
-        <v>218</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>1649</v>
+      </c>
+      <c r="D124" t="n">
+        <v>55</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -10029,28 +9152,26 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Melastomataceae</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
+          <t>Meliaceae</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>44.8795891422905</v>
+        <v>43.9688681565033</v>
       </c>
       <c r="J124" t="n">
-        <v>-27.6152814359953</v>
+        <v>-28.5017784171573</v>
       </c>
       <c r="K124" t="n">
-        <v>0.0128324732201899</v>
+        <v>0.01963926312531777</v>
       </c>
       <c r="L124" t="n">
-        <v>-1.986708788052843</v>
+        <v>0.59</v>
       </c>
       <c r="M124" t="n">
-        <v>0.4123187584396911</v>
+        <v>0.4045696117330658</v>
       </c>
       <c r="N124" t="n">
-        <v>-29.53430209877506</v>
+        <v>-30.52</v>
       </c>
       <c r="O124" t="n">
         <v>2006</v>
@@ -10062,41 +9183,32 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>p08-218</t>
-        </is>
-      </c>
-      <c r="R124" t="inlineStr"/>
+          <t>p55-1649</t>
+        </is>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>Miconia glandulistyla</t>
+          <t xml:space="preserve">Ruagea </t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>Miconia</t>
-        </is>
-      </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>glandulistyla</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
+          <t>Ruagea</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>123</v>
-      </c>
-      <c r="B125" t="inlineStr"/>
+        <v>125</v>
+      </c>
+      <c r="B125" t="n">
+        <v>8123</v>
+      </c>
       <c r="C125" t="n">
-        <v>222</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>1648</v>
+      </c>
+      <c r="D125" t="n">
+        <v>55</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -10105,28 +9217,26 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
+          <t>Chloranthaceae</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>44.4425917116135</v>
+        <v>43.2824149653684</v>
       </c>
       <c r="J125" t="n">
-        <v>-26.7875784326478</v>
+        <v>-28.2325173230001</v>
       </c>
       <c r="K125" t="n">
-        <v>0.02482700425427824</v>
+        <v>0.01931454831112982</v>
       </c>
       <c r="L125" t="n">
-        <v>-0.7</v>
+        <v>0.05</v>
       </c>
       <c r="M125" t="n">
-        <v>0.4659163218406722</v>
+        <v>0.4033671056095484</v>
       </c>
       <c r="N125" t="n">
-        <v>-29.01</v>
+        <v>-30.58</v>
       </c>
       <c r="O125" t="n">
         <v>2006</v>
@@ -10138,43 +9248,34 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>p08-222</t>
-        </is>
-      </c>
-      <c r="R125" t="inlineStr"/>
+          <t>p55-1648</t>
+        </is>
+      </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Allophylus floribundus</t>
+          <t>Hedyosmum cuatrecazanum</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>Allophylus</t>
+          <t>Hedyosmum</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>floribundus</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
+          <t>cuatrecazanum</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B126" t="n">
-        <v>8122</v>
+        <v>127</v>
       </c>
       <c r="C126" t="n">
-        <v>1649</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>1666</v>
+      </c>
+      <c r="D126" t="n">
+        <v>55</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -10183,28 +9284,26 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Meliaceae</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>43.9688681565033</v>
+        <v>42.5117491237362</v>
       </c>
       <c r="J126" t="n">
-        <v>-28.5017784171573</v>
+        <v>-29.5569165078273</v>
       </c>
       <c r="K126" t="n">
-        <v>0.01963926312531777</v>
+        <v>0.02161239227968607</v>
       </c>
       <c r="L126" t="n">
-        <v>0.59</v>
+        <v>1.47</v>
       </c>
       <c r="M126" t="n">
-        <v>0.4045696117330658</v>
+        <v>0.4095726249347134</v>
       </c>
       <c r="N126" t="n">
-        <v>-30.52</v>
+        <v>-30.51</v>
       </c>
       <c r="O126" t="n">
         <v>2006</v>
@@ -10216,39 +9315,34 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>p55-1649</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr"/>
+          <t>p55-1666</t>
+        </is>
+      </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ruagea </t>
+          <t>Palicourea corniculata</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>Ruagea</t>
-        </is>
-      </c>
-      <c r="U126" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr"/>
+          <t>Palicourea</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>corniculata</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="B127" t="n">
-        <v>8123</v>
+        <v>128</v>
       </c>
       <c r="C127" t="n">
-        <v>1648</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>1659</v>
+      </c>
+      <c r="D127" t="n">
+        <v>55</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -10257,28 +9351,26 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Chloranthaceae</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
+          <t>Myrsinaceae</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>43.2824149653684</v>
+        <v>38.0220517661371</v>
       </c>
       <c r="J127" t="n">
-        <v>-28.2325173230001</v>
+        <v>-26.7399075572636</v>
       </c>
       <c r="K127" t="n">
-        <v>0.01931454831112982</v>
+        <v>0.02159649639331145</v>
       </c>
       <c r="L127" t="n">
-        <v>0.05</v>
+        <v>2.79</v>
       </c>
       <c r="M127" t="n">
-        <v>0.4033671056095484</v>
+        <v>0.3622990403723563</v>
       </c>
       <c r="N127" t="n">
-        <v>-30.58</v>
+        <v>-27.91</v>
       </c>
       <c r="O127" t="n">
         <v>2006</v>
@@ -10290,60 +9382,66 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>p55-1648</t>
-        </is>
-      </c>
-      <c r="R127" t="inlineStr"/>
+          <t>p55-1659</t>
+        </is>
+      </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>Hedyosmum cuatrecazanum</t>
+          <t>Cybianthus occigranatensis</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>Hedyosmum</t>
+          <t>Cybianthus</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>cuatrecazanum</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
-      <c r="X127" t="inlineStr"/>
+          <t>occigranatensis</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>126</v>
-      </c>
-      <c r="B128" t="inlineStr"/>
+        <v>129</v>
+      </c>
+      <c r="B128" t="n">
+        <v>8106</v>
+      </c>
       <c r="C128" t="n">
-        <v>472</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>&lt;NA&gt;</t>
-        </is>
+        <v>1678</v>
+      </c>
+      <c r="D128" t="n">
+        <v>55</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>Guacamayos</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>41.831521425453</v>
+        <v>43.2943500023592</v>
       </c>
       <c r="J128" t="n">
-        <v>-30.9469026716087</v>
-      </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+        <v>-28.9884721792639</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.01816411719926281</v>
+      </c>
+      <c r="L128" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.4048176508759566</v>
+      </c>
+      <c r="N128" t="n">
+        <v>-30.36</v>
+      </c>
       <c r="O128" t="n">
         <v>2006</v>
       </c>
@@ -10354,29 +9452,34 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>p&lt;NA&gt;-472</t>
-        </is>
-      </c>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr"/>
-      <c r="U128" t="inlineStr"/>
-      <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
+          <t>p55-1678</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Faramea oblongifolia</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Faramea</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>oblongifolia</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>127</v>
-      </c>
-      <c r="B129" t="inlineStr"/>
+        <v>130</v>
+      </c>
       <c r="C129" t="n">
-        <v>1666</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>206</v>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -10388,25 +9491,23 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>42.5117491237362</v>
+        <v>42.0863074717965</v>
       </c>
       <c r="J129" t="n">
-        <v>-29.5569165078273</v>
+        <v>-29.5738043285129</v>
       </c>
       <c r="K129" t="n">
-        <v>0.02161239227968607</v>
+        <v>0.02912461187577434</v>
       </c>
       <c r="L129" t="n">
-        <v>1.47</v>
+        <v>0.84</v>
       </c>
       <c r="M129" t="n">
-        <v>0.4095726249347134</v>
+        <v>0.4053996693433797</v>
       </c>
       <c r="N129" t="n">
-        <v>-30.51</v>
+        <v>-30.03</v>
       </c>
       <c r="O129" t="n">
         <v>2006</v>
@@ -10418,13 +9519,12 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>p55-1666</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr"/>
+          <t>p08-206</t>
+        </is>
+      </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Palicourea corniculata</t>
+          <t>Palicourea cf andrei</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -10434,25 +9534,24 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>corniculata</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>andrei</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B130" t="inlineStr"/>
+        <v>131</v>
+      </c>
       <c r="C130" t="n">
-        <v>1659</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>1653</v>
+      </c>
+      <c r="D130" t="n">
+        <v>55</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -10461,28 +9560,26 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Myrsinaceae</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
+          <t>Actinidiaceae</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>38.0220517661371</v>
+        <v>43.4645346303749</v>
       </c>
       <c r="J130" t="n">
-        <v>-26.7399075572636</v>
+        <v>-31.1613934043707</v>
       </c>
       <c r="K130" t="n">
-        <v>0.02159649639331145</v>
+        <v>0.01743159137534957</v>
       </c>
       <c r="L130" t="n">
-        <v>2.79</v>
+        <v>2.15</v>
       </c>
       <c r="M130" t="n">
-        <v>0.3622990403723563</v>
+        <v>0.4070580967838457</v>
       </c>
       <c r="N130" t="n">
-        <v>-27.91</v>
+        <v>-32.61</v>
       </c>
       <c r="O130" t="n">
         <v>2006</v>
@@ -10494,43 +9591,42 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>p55-1659</t>
-        </is>
-      </c>
-      <c r="R130" t="inlineStr"/>
+          <t>p55-1653</t>
+        </is>
+      </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Cybianthus occigranatensis</t>
+          <t>Saurauia sp. 1</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>Cybianthus</t>
+          <t>Saurauia</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>occigranatensis</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
-      <c r="X130" t="inlineStr"/>
+          <t>sp.</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>8106</v>
+        <v>8139</v>
       </c>
       <c r="C131" t="n">
-        <v>1678</v>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>212</v>
+      </c>
+      <c r="D131" t="n">
+        <v>8</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -10539,28 +9635,26 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
+          <t>Cunoniaceae</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>43.2943500023592</v>
+        <v>40.3719427357773</v>
       </c>
       <c r="J131" t="n">
-        <v>-28.9884721792639</v>
+        <v>-29.7396234387908</v>
       </c>
       <c r="K131" t="n">
-        <v>0.01816411719926281</v>
+        <v>0.01862176770779177</v>
       </c>
       <c r="L131" t="n">
-        <v>-0.48</v>
+        <v>-2.56</v>
       </c>
       <c r="M131" t="n">
-        <v>0.4048176508759566</v>
+        <v>0.4363167965876388</v>
       </c>
       <c r="N131" t="n">
-        <v>-30.36</v>
+        <v>-31.54</v>
       </c>
       <c r="O131" t="n">
         <v>2006</v>
@@ -10572,41 +9666,34 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>p55-1678</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr"/>
+          <t>p08-212</t>
+        </is>
+      </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>Faramea oblongifolia</t>
+          <t>Weinmannia pinnata</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>Faramea</t>
+          <t>Weinmannia</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>oblongifolia</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+          <t>pinnata</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="B132" t="inlineStr"/>
+        <v>133</v>
+      </c>
       <c r="C132" t="n">
-        <v>206</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>168</v>
+      </c>
+      <c r="D132" t="n">
+        <v>6</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -10618,25 +9705,23 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>42.0863074717965</v>
+        <v>42.4081127377562</v>
       </c>
       <c r="J132" t="n">
-        <v>-29.5738043285129</v>
+        <v>-29.9530213309851</v>
       </c>
       <c r="K132" t="n">
-        <v>0.02912461187577434</v>
+        <v>0.02447277889851237</v>
       </c>
       <c r="L132" t="n">
-        <v>0.84</v>
+        <v>-0.2</v>
       </c>
       <c r="M132" t="n">
-        <v>0.4053996693433797</v>
+        <v>0.3930166920684579</v>
       </c>
       <c r="N132" t="n">
-        <v>-30.03</v>
+        <v>-29.98</v>
       </c>
       <c r="O132" t="n">
         <v>2006</v>
@@ -10648,13 +9733,12 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>p08-206</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr"/>
+          <t>p06-168</t>
+        </is>
+      </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Palicourea cf andrei</t>
+          <t>Palicourea stenosepala</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
@@ -10664,29 +9748,19 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>cf</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>andrei</t>
-        </is>
-      </c>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
+          <t>stenosepala</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>131</v>
-      </c>
-      <c r="B133" t="inlineStr"/>
+        <v>134</v>
+      </c>
       <c r="C133" t="n">
-        <v>1653</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>1654</v>
+      </c>
+      <c r="D133" t="n">
+        <v>55</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -10695,28 +9769,26 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Actinidiaceae</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>43.4645346303749</v>
+        <v>43.5121387209819</v>
       </c>
       <c r="J133" t="n">
-        <v>-31.1613934043707</v>
+        <v>-27.5488541344373</v>
       </c>
       <c r="K133" t="n">
-        <v>0.01743159137534957</v>
+        <v>0.01557489229414958</v>
       </c>
       <c r="L133" t="n">
-        <v>2.15</v>
+        <v>-1.62</v>
       </c>
       <c r="M133" t="n">
-        <v>0.4070580967838457</v>
+        <v>0.3951619002096235</v>
       </c>
       <c r="N133" t="n">
-        <v>-32.61</v>
+        <v>-29.08</v>
       </c>
       <c r="O133" t="n">
         <v>2006</v>
@@ -10728,47 +9800,37 @@
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>p55-1653</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr"/>
+          <t>p55-1654</t>
+        </is>
+      </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>Saurauia sp. 1</t>
+          <t>Faramea oblongifolia</t>
         </is>
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>Saurauia</t>
+          <t>Faramea</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>sp.</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
+          <t>oblongifolia</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>8139</v>
+        <v>8135</v>
       </c>
       <c r="C134" t="n">
-        <v>212</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>214</v>
+      </c>
+      <c r="D134" t="n">
+        <v>8</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -10777,28 +9839,26 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cunoniaceae</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+          <t>Lauraceae</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>40.3719427357773</v>
+        <v>43.6088693700159</v>
       </c>
       <c r="J134" t="n">
-        <v>-29.7396234387908</v>
+        <v>-31.6674229333118</v>
       </c>
       <c r="K134" t="n">
-        <v>0.01862176770779177</v>
+        <v>0.01920145378417257</v>
       </c>
       <c r="L134" t="n">
-        <v>-2.56</v>
+        <v>-0.31</v>
       </c>
       <c r="M134" t="n">
-        <v>0.4363167965876388</v>
+        <v>0.4634900290617749</v>
       </c>
       <c r="N134" t="n">
-        <v>-31.54</v>
+        <v>-33.48</v>
       </c>
       <c r="O134" t="n">
         <v>2006</v>
@@ -10810,41 +9870,34 @@
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>p08-212</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr"/>
+          <t>p08-214</t>
+        </is>
+      </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>Weinmannia pinnata</t>
+          <t>Cryptocarya aschersoniana</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>Weinmannia</t>
+          <t>Cryptocarya</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>pinnata</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
+          <t>aschersoniana</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>133</v>
-      </c>
-      <c r="B135" t="inlineStr"/>
+        <v>136</v>
+      </c>
       <c r="C135" t="n">
-        <v>168</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>1645</v>
+      </c>
+      <c r="D135" t="n">
+        <v>55</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -10856,25 +9909,23 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>42.4081127377562</v>
+        <v>43.6240424137866</v>
       </c>
       <c r="J135" t="n">
-        <v>-29.9530213309851</v>
+        <v>-30.5377543510784</v>
       </c>
       <c r="K135" t="n">
-        <v>0.02447277889851237</v>
+        <v>0.02703386443962728</v>
       </c>
       <c r="L135" t="n">
-        <v>-0.2</v>
+        <v>1.88</v>
       </c>
       <c r="M135" t="n">
-        <v>0.3930166920684579</v>
+        <v>0.3950691828828367</v>
       </c>
       <c r="N135" t="n">
-        <v>-29.98</v>
+        <v>-31.17</v>
       </c>
       <c r="O135" t="n">
         <v>2006</v>
@@ -10886,10 +9937,9 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>p06-168</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr"/>
+          <t>p55-1645</t>
+        </is>
+      </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>Palicourea stenosepala</t>
@@ -10905,22 +9955,16 @@
           <t>stenosepala</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>134</v>
-      </c>
-      <c r="B136" t="inlineStr"/>
+        <v>137</v>
+      </c>
       <c r="C136" t="n">
-        <v>1654</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>1672</v>
+      </c>
+      <c r="D136" t="n">
+        <v>55</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -10929,28 +9973,26 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+          <t>Actinidiaceae</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>43.5121387209819</v>
+        <v>42.3664417049092</v>
       </c>
       <c r="J136" t="n">
-        <v>-27.5488541344373</v>
+        <v>-27.4103398577115</v>
       </c>
       <c r="K136" t="n">
-        <v>0.01557489229414958</v>
+        <v>0.02034099942167312</v>
       </c>
       <c r="L136" t="n">
-        <v>-1.62</v>
+        <v>-0.66</v>
       </c>
       <c r="M136" t="n">
-        <v>0.3951619002096235</v>
+        <v>0.4441091347112673</v>
       </c>
       <c r="N136" t="n">
-        <v>-29.08</v>
+        <v>-29.38</v>
       </c>
       <c r="O136" t="n">
         <v>2006</v>
@@ -10962,43 +10004,42 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>p55-1654</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr"/>
+          <t>p55-1672</t>
+        </is>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>Faramea oblongifolia</t>
+          <t>Saurauia sp. 1</t>
         </is>
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>Faramea</t>
+          <t>Saurauia</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>oblongifolia</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
+          <t>sp.</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>8135</v>
+        <v>8150</v>
       </c>
       <c r="C137" t="n">
-        <v>214</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
+        <v>183</v>
+      </c>
+      <c r="D137" t="n">
+        <v>7</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -11007,28 +10048,26 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>43.6088693700159</v>
+        <v>41.02</v>
       </c>
       <c r="J137" t="n">
-        <v>-31.6674229333118</v>
+        <v>-30.2</v>
       </c>
       <c r="K137" t="n">
-        <v>0.01920145378417257</v>
+        <v>0.02797968727764726</v>
       </c>
       <c r="L137" t="n">
-        <v>-0.31</v>
+        <v>3.78</v>
       </c>
       <c r="M137" t="n">
-        <v>0.4634900290617749</v>
+        <v>0.4353886256530883</v>
       </c>
       <c r="N137" t="n">
-        <v>-33.48</v>
+        <v>-32.02</v>
       </c>
       <c r="O137" t="n">
         <v>2006</v>
@@ -11040,41 +10079,37 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>p08-214</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr"/>
+          <t>p07-183</t>
+        </is>
+      </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>Cryptocarya aschersoniana</t>
+          <t>Joosia umbellifera</t>
         </is>
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>Cryptocarya</t>
+          <t>Joosia</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>aschersoniana</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
-      <c r="X137" t="inlineStr"/>
+          <t>umbellifera</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B138" t="inlineStr"/>
+        <v>139</v>
+      </c>
+      <c r="B138" t="n">
+        <v>8150</v>
+      </c>
       <c r="C138" t="n">
-        <v>1645</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>183</v>
+      </c>
+      <c r="D138" t="n">
+        <v>7</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -11086,25 +10121,23 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="n">
-        <v>43.6240424137866</v>
+        <v>41.02</v>
       </c>
       <c r="J138" t="n">
-        <v>-30.5377543510784</v>
+        <v>-30.2</v>
       </c>
       <c r="K138" t="n">
-        <v>0.02703386443962728</v>
+        <v>0.02019997804176686</v>
       </c>
       <c r="L138" t="n">
-        <v>1.88</v>
+        <v>2.017886272257323</v>
       </c>
       <c r="M138" t="n">
-        <v>0.3950691828828367</v>
+        <v>0.3253214887991884</v>
       </c>
       <c r="N138" t="n">
-        <v>-31.17</v>
+        <v>-28.07851681360693</v>
       </c>
       <c r="O138" t="n">
         <v>2006</v>
@@ -11116,41 +10149,37 @@
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>p55-1645</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr"/>
+          <t>p07-183</t>
+        </is>
+      </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>Palicourea stenosepala</t>
+          <t>Joosia umbellifera</t>
         </is>
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>Palicourea</t>
+          <t>Joosia</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>stenosepala</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
+          <t>umbellifera</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="B139" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="B139" t="n">
+        <v>8150</v>
+      </c>
       <c r="C139" t="n">
-        <v>1672</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+        <v>183</v>
+      </c>
+      <c r="D139" t="n">
+        <v>7</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -11159,28 +10188,26 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Actinidiaceae</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>42.3664417049092</v>
+        <v>41.02</v>
       </c>
       <c r="J139" t="n">
-        <v>-27.4103398577115</v>
+        <v>-30.2</v>
       </c>
       <c r="K139" t="n">
-        <v>0.02034099942167312</v>
+        <v>0.02938196230007473</v>
       </c>
       <c r="L139" t="n">
-        <v>-0.66</v>
+        <v>4.020183802412406</v>
       </c>
       <c r="M139" t="n">
-        <v>0.4441091347112673</v>
+        <v>0.4221344425150206</v>
       </c>
       <c r="N139" t="n">
-        <v>-29.38</v>
+        <v>-32.21653663103691</v>
       </c>
       <c r="O139" t="n">
         <v>2006</v>
@@ -11192,45 +10219,37 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>p55-1672</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr"/>
+          <t>p07-183</t>
+        </is>
+      </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>Saurauia sp. 1</t>
+          <t>Joosia umbellifera</t>
         </is>
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>Saurauia</t>
+          <t>Joosia</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>sp.</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
+          <t>umbellifera</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>138</v>
-      </c>
-      <c r="B140" t="inlineStr"/>
+        <v>141</v>
+      </c>
+      <c r="B140" t="n">
+        <v>8186</v>
+      </c>
       <c r="C140" t="n">
-        <v>183</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>157</v>
+      </c>
+      <c r="D140" t="n">
+        <v>6</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -11239,74 +10258,63 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+          <t>Euphorbiaceae</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>41.02</v>
+        <v>42.92</v>
       </c>
       <c r="J140" t="n">
-        <v>-30.2</v>
+        <v>-28.53</v>
       </c>
       <c r="K140" t="n">
-        <v>0.02797968727764726</v>
+        <v>0.03645078452623074</v>
       </c>
       <c r="L140" t="n">
-        <v>3.78</v>
+        <v>5.87</v>
       </c>
       <c r="M140" t="n">
-        <v>0.4353886256530883</v>
+        <v>0.4161364593228006</v>
       </c>
       <c r="N140" t="n">
-        <v>-32.02</v>
+        <v>-28.58</v>
       </c>
       <c r="O140" t="n">
         <v>2006</v>
       </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>p07-183</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr"/>
+          <t>p06-157</t>
+        </is>
+      </c>
+      <c r="R140" t="n">
+        <v>42.92</v>
+      </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>Joosia umbellifera</t>
+          <t>Sapium stylare</t>
         </is>
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>Joosia</t>
+          <t>Sapium</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>umbellifera</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
+          <t>stylare</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="B141" t="inlineStr"/>
+        <v>142</v>
+      </c>
       <c r="C141" t="n">
-        <v>183</v>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>669</v>
+      </c>
+      <c r="D141" t="n">
+        <v>27</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -11315,74 +10323,56 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
+          <t>Meliaceae</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>41.02</v>
+        <v>41.43</v>
       </c>
       <c r="J141" t="n">
-        <v>-30.2</v>
-      </c>
-      <c r="K141" t="n">
-        <v>0.02019997804176686</v>
-      </c>
-      <c r="L141" t="n">
-        <v>2.017886272257323</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0.3253214887991884</v>
-      </c>
-      <c r="N141" t="n">
-        <v>-28.07851681360693</v>
+        <v>-29.16</v>
       </c>
       <c r="O141" t="n">
         <v>2006</v>
       </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>p07-183</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr"/>
+          <t>p27-669</t>
+        </is>
+      </c>
+      <c r="R141" t="n">
+        <v>41.43</v>
+      </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>Joosia umbellifera</t>
+          <t>Ruagea cf ovalis</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>Joosia</t>
+          <t>Ruagea</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>umbellifera</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>ovalis</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B142" t="inlineStr"/>
+        <v>143</v>
+      </c>
       <c r="C142" t="n">
-        <v>183</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
+        <v>682</v>
+      </c>
+      <c r="D142" t="n">
+        <v>27</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -11391,76 +10381,56 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+          <t>Meliaceae</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>41.02</v>
+        <v>38.34</v>
       </c>
       <c r="J142" t="n">
-        <v>-30.2</v>
-      </c>
-      <c r="K142" t="n">
-        <v>0.02938196230007473</v>
-      </c>
-      <c r="L142" t="n">
-        <v>4.020183802412406</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0.4221344425150206</v>
-      </c>
-      <c r="N142" t="n">
-        <v>-32.21653663103691</v>
+        <v>-30.45</v>
       </c>
       <c r="O142" t="n">
         <v>2006</v>
       </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>leaf pulverized</t>
-        </is>
-      </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>p07-183</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr"/>
+          <t>p27-682</t>
+        </is>
+      </c>
+      <c r="R142" t="n">
+        <v>38.34</v>
+      </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>Joosia umbellifera</t>
+          <t>Ruagea cf ovalis</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>Joosia</t>
+          <t>Ruagea</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>umbellifera</t>
-        </is>
-      </c>
-      <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>ovalis</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>141</v>
-      </c>
-      <c r="B143" t="n">
-        <v>8186</v>
+        <v>144</v>
       </c>
       <c r="C143" t="n">
-        <v>157</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
+        <v>687</v>
+      </c>
+      <c r="D143" t="n">
+        <v>27</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -11472,69 +10442,43 @@
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="n">
-        <v>42.92</v>
+        <v>44.76</v>
       </c>
       <c r="J143" t="n">
-        <v>-28.53</v>
-      </c>
-      <c r="K143" t="n">
-        <v>0.03645078452623074</v>
-      </c>
-      <c r="L143" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0.4161364593228006</v>
-      </c>
-      <c r="N143" t="n">
-        <v>-28.58</v>
+        <v>-31.23</v>
       </c>
       <c r="O143" t="n">
         <v>2006</v>
       </c>
-      <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>p06-157</t>
+          <t>p27-687</t>
         </is>
       </c>
       <c r="R143" t="n">
-        <v>42.92</v>
+        <v>44.76</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Sapium stylare</t>
+          <t xml:space="preserve">Margaritaria </t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>Sapium</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>stylare</t>
-        </is>
-      </c>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr"/>
+          <t>Margaritaria</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>142</v>
-      </c>
-      <c r="B144" t="inlineStr"/>
+        <v>145</v>
+      </c>
       <c r="C144" t="n">
-        <v>669</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+        <v>694</v>
+      </c>
+      <c r="D144" t="n">
+        <v>27</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -11543,68 +10487,51 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Meliaceae</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>41.43</v>
+        <v>42.36</v>
       </c>
       <c r="J144" t="n">
-        <v>-29.16</v>
-      </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+        <v>-28.27</v>
+      </c>
       <c r="O144" t="n">
         <v>2006</v>
       </c>
-      <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>p27-669</t>
+          <t>p27-694</t>
         </is>
       </c>
       <c r="R144" t="n">
-        <v>41.43</v>
+        <v>42.36</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Ruagea cf ovalis</t>
+          <t>Joosia umbellifera</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>Ruagea</t>
+          <t>Joosia</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>cf</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>ovalis</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
+          <t>umbellifera</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>143</v>
-      </c>
-      <c r="B145" t="inlineStr"/>
+        <v>146</v>
+      </c>
       <c r="C145" t="n">
-        <v>682</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+        <v>695</v>
+      </c>
+      <c r="D145" t="n">
+        <v>27</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -11613,68 +10540,51 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Meliaceae</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>38.34</v>
+        <v>41.82</v>
       </c>
       <c r="J145" t="n">
-        <v>-30.45</v>
-      </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+        <v>-30.34</v>
+      </c>
       <c r="O145" t="n">
         <v>2006</v>
       </c>
-      <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>p27-682</t>
+          <t>p27-695</t>
         </is>
       </c>
       <c r="R145" t="n">
-        <v>38.34</v>
+        <v>41.82</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>Ruagea cf ovalis</t>
+          <t>Joosia umbellifera</t>
         </is>
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>Ruagea</t>
+          <t>Joosia</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>cf</t>
-        </is>
-      </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>ovalis</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr"/>
-      <c r="X145" t="inlineStr"/>
+          <t>umbellifera</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B146" t="inlineStr"/>
+        <v>147</v>
+      </c>
       <c r="C146" t="n">
-        <v>687</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+        <v>696</v>
+      </c>
+      <c r="D146" t="n">
+        <v>27</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -11683,60 +10593,46 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>44.76</v>
+        <v>41.83</v>
       </c>
       <c r="J146" t="n">
-        <v>-31.23</v>
-      </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+        <v>-25.96</v>
+      </c>
       <c r="O146" t="n">
         <v>2006</v>
       </c>
-      <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>p27-687</t>
+          <t>p27-696</t>
         </is>
       </c>
       <c r="R146" t="n">
-        <v>44.76</v>
+        <v>41.83</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margaritaria </t>
+          <t xml:space="preserve">Elaeagia </t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>Margaritaria</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr"/>
-      <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr"/>
+          <t>Elaeagia</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>145</v>
-      </c>
-      <c r="B147" t="inlineStr"/>
+        <v>148</v>
+      </c>
       <c r="C147" t="n">
-        <v>694</v>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+        <v>704</v>
+      </c>
+      <c r="D147" t="n">
+        <v>27</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -11748,61 +10644,53 @@
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="n">
-        <v>42.36</v>
+        <v>42.18</v>
       </c>
       <c r="J147" t="n">
-        <v>-28.27</v>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+        <v>-30.11</v>
+      </c>
       <c r="O147" t="n">
         <v>2006</v>
       </c>
-      <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>p27-694</t>
+          <t>p27-704</t>
         </is>
       </c>
       <c r="R147" t="n">
-        <v>42.36</v>
+        <v>42.18</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>Joosia umbellifera</t>
+          <t>Palicourea cf andrei</t>
         </is>
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>Joosia</t>
+          <t>Palicourea</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>umbellifera</t>
-        </is>
-      </c>
-      <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
+          <t>cf</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>andrei</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>146</v>
-      </c>
-      <c r="B148" t="inlineStr"/>
+        <v>149</v>
+      </c>
       <c r="C148" t="n">
-        <v>695</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+        <v>708</v>
+      </c>
+      <c r="D148" t="n">
+        <v>27</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -11811,64 +10699,61 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+          <t>Clethraceae</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>41.82</v>
+        <v>42.26</v>
       </c>
       <c r="J148" t="n">
-        <v>-30.34</v>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+        <v>-30.48</v>
+      </c>
       <c r="O148" t="n">
         <v>2006</v>
       </c>
-      <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>p27-695</t>
+          <t>p27-708</t>
         </is>
       </c>
       <c r="R148" t="n">
-        <v>41.82</v>
+        <v>42.26</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>Joosia umbellifera</t>
+          <t xml:space="preserve">Clethra fagifolia var fagifolia </t>
         </is>
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>Joosia</t>
+          <t>Clethra</t>
         </is>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>umbellifera</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr"/>
+          <t>fagifolia</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>var</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>fagifolia</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>147</v>
-      </c>
-      <c r="B149" t="inlineStr"/>
+        <v>150</v>
+      </c>
       <c r="C149" t="n">
-        <v>696</v>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+        <v>712</v>
+      </c>
+      <c r="D149" t="n">
+        <v>27</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -11877,60 +10762,51 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
+          <t>Sapotaceae</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>41.83</v>
+        <v>42.31</v>
       </c>
       <c r="J149" t="n">
-        <v>-25.96</v>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+        <v>-28.23</v>
+      </c>
       <c r="O149" t="n">
         <v>2006</v>
       </c>
-      <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>p27-696</t>
+          <t>p27-712</t>
         </is>
       </c>
       <c r="R149" t="n">
-        <v>41.83</v>
+        <v>42.31</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elaeagia </t>
+          <t>Pouteria baehniana</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>Elaeagia</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr"/>
-      <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
-      <c r="X149" t="inlineStr"/>
+          <t>Pouteria</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>baehniana</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B150" t="inlineStr"/>
+        <v>151</v>
+      </c>
       <c r="C150" t="n">
-        <v>704</v>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+        <v>714</v>
+      </c>
+      <c r="D150" t="n">
+        <v>27</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -11939,261 +10815,41 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
+          <t>Myrsinaceae</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>42.18</v>
+        <v>44.86</v>
       </c>
       <c r="J150" t="n">
-        <v>-30.11</v>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+        <v>-30.17</v>
+      </c>
       <c r="O150" t="n">
         <v>2006</v>
       </c>
-      <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>p27-704</t>
+          <t>p27-714</t>
         </is>
       </c>
       <c r="R150" t="n">
-        <v>42.18</v>
+        <v>44.86</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>Palicourea cf andrei</t>
+          <t>Myrsine coriaceae</t>
         </is>
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>Palicourea</t>
+          <t>Myrsine</t>
         </is>
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>cf</t>
-        </is>
-      </c>
-      <c r="V150" t="inlineStr">
-        <is>
-          <t>andrei</t>
-        </is>
-      </c>
-      <c r="W150" t="inlineStr"/>
-      <c r="X150" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="n">
-        <v>708</v>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Guacamayos</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Clethraceae</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="n">
-        <v>42.26</v>
-      </c>
-      <c r="J151" t="n">
-        <v>-30.48</v>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="n">
-        <v>2006</v>
-      </c>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>p27-708</t>
-        </is>
-      </c>
-      <c r="R151" t="n">
-        <v>42.26</v>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clethra fagifolia var fagifolia </t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>Clethra</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>fagifolia</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>var</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>fagifolia</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="n">
-        <v>712</v>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Guacamayos</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>Sapotaceae</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="J152" t="n">
-        <v>-28.23</v>
-      </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="n">
-        <v>2006</v>
-      </c>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>p27-712</t>
-        </is>
-      </c>
-      <c r="R152" t="n">
-        <v>42.31</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>Pouteria baehniana</t>
-        </is>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>baehniana</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
-      <c r="X152" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>151</v>
-      </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="n">
-        <v>714</v>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Guacamayos</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Myrsinaceae</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="n">
-        <v>44.86</v>
-      </c>
-      <c r="J153" t="n">
-        <v>-30.17</v>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="n">
-        <v>2006</v>
-      </c>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr">
-        <is>
-          <t>p27-714</t>
-        </is>
-      </c>
-      <c r="R153" t="n">
-        <v>44.86</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>Myrsine coriaceae</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>Myrsine</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
           <t>coriaceae</t>
         </is>
       </c>
-      <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
